--- a/consolidado.xlsx
+++ b/consolidado.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1505" uniqueCount="583">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1531" uniqueCount="578">
   <si>
     <t>SGE</t>
   </si>
@@ -1036,6 +1036,9 @@
     <t>BR-020;BR-020;CE-277;CE-277;Estrada Santa Rita;CE-279</t>
   </si>
   <si>
+    <t>BR-020;CE-279;Estrada Santa Rita;CE-277;BR-020;CE-277</t>
+  </si>
+  <si>
     <t>BR-020;CE-266;OSM-tertiary;Estrada para Boa Viagem;Rua Luiz Vieira de Sousa;Rua José Vieira Neto;Rua Belarmino Matos Carneiro</t>
   </si>
   <si>
@@ -1075,18 +1078,24 @@
     <t>BR-222;CE-321;CE-253;BR-403;CE-183</t>
   </si>
   <si>
+    <t>BR-222;CE-321;CE-253;CE-321;CE-253;Avenida Manoel Silvino;OSM-tertiary;Travessa Padre Moacir Melo;Rua Domingos Ferreira;Rua Sebastião de Almeida;CE-581;Rua Capitão Joaquim Francisco;OSM-secondary</t>
+  </si>
+  <si>
     <t>BR-222;OSM-secondary;Rua Capitão Joaquim Francisco;CE-581;Rua Sebastião de Almeida;Rua Domingos Ferreira;Travessa Padre Moacir Melo;OSM-tertiary;CE-253;Avenida Manoel Silvino;CE-321;CE-253;CE-321</t>
   </si>
   <si>
+    <t>BR-222;OSM-secondary;Rua Capitão Joaquim Francisco;CE-581</t>
+  </si>
+  <si>
     <t>BR-222;CE-581;Rua Capitão Joaquim Francisco;OSM-secondary</t>
   </si>
   <si>
+    <t>BR-222;CE-581;Rua Sebastião de Almeida;Rua Domingos Ferreira;Travessa Padre Moacir Melo;OSM-tertiary;CE-253;CE-187;OSM-primary_link;Avenida Prefeito Jacques Nunes</t>
+  </si>
+  <si>
     <t>BR-222;Avenida Prefeito Jacques Nunes;CE-187;OSM-primary_link;CE-253;OSM-tertiary;Travessa Padre Moacir Melo;Rua Domingos Ferreira;Rua Sebastião de Almeida;CE-581</t>
   </si>
   <si>
-    <t>BR-222;CE-581;Rua Sebastião de Almeida;Rua Domingos Ferreira;Travessa Padre Moacir Melo;OSM-tertiary;CE-253;CE-187;OSM-primary_link;Avenida Prefeito Jacques Nunes</t>
-  </si>
-  <si>
     <t>Avenida Prefeito Jacques Nunes;Rua Francisco Teles;Avenida Moisés Moita;CE-418;BR-222</t>
   </si>
   <si>
@@ -1099,75 +1108,87 @@
     <t>BR-222;CE-187;OSM-trunk</t>
   </si>
   <si>
+    <t>BR-222;CE-348;Estrada da Área da Petrobrás;OSM-tertiary;OSM-trunk_link;CE-085;CE-156</t>
+  </si>
+  <si>
+    <t>BR-222;CE-423;Avenida Coronel Neco Martins;Rua Eretildes Martins;Avenida Paulo Costa;CE-085;OSM-tertiary;CE-156;BR-222;CE-156</t>
+  </si>
+  <si>
+    <t>BR-402;CE-240;BR-402;CE-354;Rua Antônio Manoel Alves;Rua Joaquim Rodrigues Teixeira de Menezes;OSM-tertiary;Rua Principal;Rua do Salão;CE-173;CE-240</t>
+  </si>
+  <si>
+    <t>BR-402;CE-354;CE-354;OSM-tertiary</t>
+  </si>
+  <si>
+    <t>BR-402;CE-354;OSM-tertiary;OSM-secondary</t>
+  </si>
+  <si>
+    <t>BR-402;CE-354;OSM-secondary;CE-354;URB-010;Avenida Artur Rodrigues Vasconcelos;Rua Marcolino Evangelista;Rua João Galdino Vasconcelos;Rua Coronel João Antônio;CE-139;URB-030;CE-333</t>
+  </si>
+  <si>
+    <t>BR-402;CE-354;CE-333;CE-139;URB-030;Rua Coronel João Antônio;Rua João Galdino Vasconcelos;Rua Marcolino Evangelista;Avenida Artur Rodrigues Vasconcelos;CE-354;URB-010;OSM-secondary</t>
+  </si>
+  <si>
+    <t>BR-402;CE-354;Rua Antônio Pires;CE-333;OSM-tertiary;URB-253;Estrada para o Tururu</t>
+  </si>
+  <si>
+    <t>BR-402;CE-243;CE-354;OSM-tertiary;CE-354;Rua Walter Moraes;Rua Francisco Gomes dos Santos;Rua José Alexandre;Rua Felisbela Caetano;BR-222;CE-235</t>
+  </si>
+  <si>
+    <t>BR-222;CE-176;CE-362;Avenida Tabelião Joaquim José Rodrigues;Rua Raimundo Nonato de Loiola</t>
+  </si>
+  <si>
+    <t>BR-222;CE-176;OSM-tertiary</t>
+  </si>
+  <si>
+    <t>BR-222;CE-173;CE-240;OSM-primary;Rua Dezinho Teixeira;OSM-tertiary;Rua Luiz Matias;Avenida Lindolfo Braga;CE-176;Rodovia Doutor José Euclides Ferreira Gomes Júnior;OSM-trunk_link</t>
+  </si>
+  <si>
+    <t>BR-222;OSM-trunk_link;CE-176;Rodovia Doutor José Euclides Ferreira Gomes Júnior;Avenida Lindolfo Braga;Rua Luiz Matias;CE-240;OSM-tertiary;Rua Dezinho Teixeira;OSM-primary;CE-173</t>
+  </si>
+  <si>
+    <t>BR-222;CE-173;Rua Principal;OSM-tertiary;Rua Joaquim Rodrigues Teixeira de Menezes;Rua Urbano Teixeira de Menezes;BR-402;CE-354;CE-168;CE-333;URB-178;URB-070;CE-243;URB-060;CE-243;Rua Fausto Pinheiro;Rua Manoel Luiz da Rocha;Rua Major João Ribeiro;Rua Major Joaquim Alexandre;OSM-trunk_link;Avenida Paulo Bastos</t>
+  </si>
+  <si>
+    <t>BR-222;OSM-trunk_link;Avenida Paulo Bastos;CE-173;Rua Principal;OSM-tertiary;Rua Joaquim Rodrigues Teixeira de Menezes;Rua Urbano Teixeira de Menezes;BR-402;CE-354;CE-168;CE-333;URB-178;URB-070;CE-243;URB-060;CE-243;Rua Fausto Pinheiro;Rua Manoel Luiz da Rocha;Rua Major João Ribeiro;Rua Major Joaquim Alexandre</t>
+  </si>
+  <si>
+    <t>BR-222;CE-243;Rua Major Joaquim Alexandre;Rua Major João Ribeiro;Rua Manoel Luiz da Rocha;Rua Fausto Pinheiro;CE-243;URB-060;URB-178;URB-070;CE-333;CE-168;BR-402;CE-354;Rua Urbano Teixeira de Menezes;Rua Joaquim Rodrigues Teixeira de Menezes;OSM-tertiary;Rua Principal;CE-173;Avenida Paulo Bastos;OSM-trunk_link</t>
+  </si>
+  <si>
+    <t>BR-222;CE-168;Rua Antônio Braga;Rua Francisco José de Oliveira;OSM-tertiary;CE-243</t>
+  </si>
+  <si>
+    <t>BR-222;OSM-tertiary;CE-243;Rua Francisco José de Oliveira;Rua Antônio Braga;CE-168</t>
+  </si>
+  <si>
+    <t>BR-222;OSM-tertiary</t>
+  </si>
+  <si>
+    <t>BR-222;CE-168;OSM-tertiary</t>
+  </si>
+  <si>
+    <t>BR-222;Avenida Cruzeiro do Sul;Rua Coronel Correia;Rua Barão de Ibiapaba;Avenida da Integração;Avenida Contorno Norte;BR-020;BR-222;OSM-trunk_link</t>
+  </si>
+  <si>
+    <t>BR-222;Avenida Cruzeiro do Sul;Rua José Holanda Nogueira;CE-085;Estrada do Garrote;Estrada Garrote;OSM-tertiary</t>
+  </si>
+  <si>
+    <t>BR-222;CE-348;Estrada Garrote;OSM-tertiary</t>
+  </si>
+  <si>
     <t>BR-222;CE-156;CE-085;OSM-trunk_link;OSM-tertiary;Estrada da Área da Petrobrás;CE-348</t>
   </si>
   <si>
-    <t>BR-222;CE-423;Avenida Coronel Neco Martins;Rua Eretildes Martins;Avenida Paulo Costa;CE-085;OSM-tertiary;CE-156;BR-222;CE-156</t>
-  </si>
-  <si>
-    <t>BR-402;CE-240;BR-402;CE-354;Rua Antônio Manoel Alves;Rua Joaquim Rodrigues Teixeira de Menezes;OSM-tertiary;Rua Principal;Rua do Salão;CE-173;CE-240</t>
-  </si>
-  <si>
-    <t>BR-402;CE-354;CE-354;OSM-tertiary</t>
-  </si>
-  <si>
-    <t>BR-402;CE-354;OSM-secondary;OSM-tertiary</t>
-  </si>
-  <si>
-    <t>BR-402;CE-354;OSM-secondary;CE-354;URB-010;Avenida Artur Rodrigues Vasconcelos;Rua Marcolino Evangelista;Rua João Galdino Vasconcelos;Rua Coronel João Antônio;CE-139;URB-030;CE-333</t>
-  </si>
-  <si>
-    <t>BR-402;CE-354;Rua Antônio Pires;CE-333;OSM-tertiary;URB-253;Estrada para o Tururu</t>
-  </si>
-  <si>
-    <t>BR-402;BR-222;CE-235;CE-354;Rua Felisbela Caetano;Rua José Alexandre;Rua Francisco Gomes dos Santos;Rua Walter Moraes;OSM-tertiary;CE-243;CE-354</t>
-  </si>
-  <si>
-    <t>BR-222;CE-176;CE-362;Avenida Tabelião Joaquim José Rodrigues;Rua Raimundo Nonato de Loiola</t>
-  </si>
-  <si>
-    <t>BR-222;CE-176;OSM-tertiary</t>
-  </si>
-  <si>
-    <t>BR-222;OSM-trunk_link;CE-176;Rodovia Doutor José Euclides Ferreira Gomes Júnior;Avenida Lindolfo Braga;Rua Luiz Matias;CE-240;OSM-tertiary;Rua Dezinho Teixeira;OSM-primary;CE-173</t>
-  </si>
-  <si>
-    <t>BR-222;CE-173;CE-240;OSM-primary;Rua Dezinho Teixeira;OSM-tertiary;Rua Luiz Matias;Avenida Lindolfo Braga;CE-176;Rodovia Doutor José Euclides Ferreira Gomes Júnior;OSM-trunk_link</t>
-  </si>
-  <si>
-    <t>BR-222;Avenida Paulo Bastos;OSM-trunk_link;CE-243;Rua Major Joaquim Alexandre;Rua Major João Ribeiro;Rua Manoel Luiz da Rocha;Rua Fausto Pinheiro;CE-243;URB-060;URB-178;URB-070;CE-333;CE-168;BR-402;CE-354;Rua Urbano Teixeira de Menezes;Rua Joaquim Rodrigues Teixeira de Menezes;OSM-tertiary;Rua Principal;CE-173</t>
-  </si>
-  <si>
-    <t>BR-222;CE-243;Rua Major Joaquim Alexandre;Rua Major João Ribeiro;Rua Manoel Luiz da Rocha;Rua Fausto Pinheiro;CE-243;URB-060;URB-178;URB-070;CE-333;CE-168;BR-402;CE-354;Rua Urbano Teixeira de Menezes;Rua Joaquim Rodrigues Teixeira de Menezes;OSM-tertiary;Rua Principal;CE-173;Avenida Paulo Bastos;OSM-trunk_link</t>
-  </si>
-  <si>
-    <t>BR-222;CE-168;Rua Antônio Braga;Rua Francisco José de Oliveira;OSM-tertiary;CE-243</t>
-  </si>
-  <si>
-    <t>OSM-tertiary;CE-168;BR-222</t>
-  </si>
-  <si>
-    <t>BR-222;OSM-tertiary;CE-168</t>
-  </si>
-  <si>
-    <t>BR-222;Avenida Cruzeiro do Sul;Rua Coronel Correia;Rua Barão de Ibiapaba;Avenida da Integração;Avenida Contorno Norte;BR-020;BR-222;OSM-trunk_link</t>
-  </si>
-  <si>
-    <t>BR-222;Avenida Cruzeiro do Sul;Rua José Holanda Nogueira;CE-085;Estrada do Garrote;Estrada Garrote;OSM-tertiary</t>
-  </si>
-  <si>
-    <t>BR-222;CE-348;Estrada Garrote;OSM-tertiary</t>
-  </si>
-  <si>
-    <t>BR-222;CE-348;Estrada da Área da Petrobrás;OSM-tertiary;OSM-trunk_link;CE-085;CE-156</t>
-  </si>
-  <si>
     <t>BR-222;Estrada Croatá-Pentecoste;CE-341;OSM-primary_link;CE-426;CE-162;Rua Rochael Moreira;Rua Prudencio Bezerra;Rua Pedro Cipriano;Avenida Pedro Cipriano</t>
   </si>
   <si>
     <t>BR-222;CE-235;CE-354;CE-162;Rua Padre Sinval Facundo;CE-341;CE-354;CE-341;OSM-primary</t>
   </si>
   <si>
+    <t>BR-222;OSM-primary;CE-341;CE-341;CE-354;Rua Padre Sinval Facundo;CE-162;CE-354;CE-235</t>
+  </si>
+  <si>
     <t>BR-222;BR-402;CE-243;CE-354;OSM-tertiary;CE-354;Rua Walter Moraes;Rua Francisco Gomes dos Santos;Rua José Alexandre;Rua Felisbela Caetano;CE-235</t>
   </si>
   <si>
@@ -1204,12 +1225,15 @@
     <t>BR-116;OSM-trunk_link;CE-282;BR-404;CE-282;CE-153;BR-404;CE-282;CE-153;CE-284;OSM-tertiary</t>
   </si>
   <si>
+    <t>BR-116;CE-284;BR-116;BR-230;Rua Luis Jacinto;Rua Coronel João Augusto;OSM-tertiary;CE-153;CE-284</t>
+  </si>
+  <si>
+    <t>BR-116;Rua Chico Pitombeira;OSM-trunk_link;OSM-primary;CE-282;Avenida Josefa Nogueira Monteiro;BR-404;CE-282;CE-153;Rua da Residencia;Rua Custódio Nunes;Rua José Matos Leite;OSM-tertiary;Avenida Joaquim Távora;CE-275</t>
+  </si>
+  <si>
     <t>BR-116;CE-284;OSM-tertiary;CE-284;CE-153;Rua Coronel João Augusto;Rua Luis Jacinto;BR-230;BR-116</t>
   </si>
   <si>
-    <t>BR-116;Rua Chico Pitombeira;OSM-trunk_link;OSM-primary;CE-282;Avenida Josefa Nogueira Monteiro;BR-404;CE-282;CE-153;Rua da Residencia;Rua Custódio Nunes;Rua José Matos Leite;OSM-tertiary;Avenida Joaquim Távora;CE-275</t>
-  </si>
-  <si>
     <t>BR-116;Rua Chico Pitombeira;OSM-primary;BR-226;CE-138;Estrada de São Miguel A Pereira;Rua Manoel Queijo;Rua Manuel Queijo;Rua Milton Franca;Rua Doutor José Torquato;RN-177;OSM-tertiary;OSM-secondary;Rua Nova;Rua Diamante;CE-282;OSM-trunk_link</t>
   </si>
   <si>
@@ -1225,6 +1249,9 @@
     <t>BR-230;OSM-tertiary;Desembargador Haroldo Correia de Oliveira Maximo;CE-166;BR-230;CE-489</t>
   </si>
   <si>
+    <t>BR-230;Rua Luis Jacinto;Rua Coronel João Augusto;OSM-tertiary;CE-153;CE-284;BR-116;CE-284;BR-116</t>
+  </si>
+  <si>
     <t>BR-230;OSM-tertiary;CE-153;BR-230;CE-153</t>
   </si>
   <si>
@@ -1240,7 +1267,7 @@
     <t>BR-230;OSM-tertiary;Desembargador Haroldo Correia de Oliveira Maximo;CE-166</t>
   </si>
   <si>
-    <t>BR-230;OSM-tertiary;CE-166;OSM-secondary;CE-284;BR-122;CE-060;CE-060</t>
+    <t>BR-230;CE-060;BR-122;CE-060;CE-284;CE-166;OSM-secondary;OSM-tertiary</t>
   </si>
   <si>
     <t>CE-275;BR-226;CE-368;CE-368;CE-371;Estrada para Jaguaribe;Rua José Guerra;Avenida do Contorno;Avenida Governador Manoel de Castro Filho;CE-269;OSM-secondary_link;CE-546;Avenida Vereador Sobrinho;OSM-secondary;BR-116;Rua Sigefredo Diógenes;Rua da Rodoviaria 2;Rua Savino Barreira;Avenida GIl Teixeira Bastos;Rua Gil Teixeira Bastos</t>
@@ -1255,6 +1282,9 @@
     <t>BR-226;Rua Audízio Vieira do Nascimento;Rua Pedro II;Rua Franco Magalhães;Rua José Benigno Soares;Rua Antônio Soares;Rua Sisgismundo Rodrigues;OSM-tertiary</t>
   </si>
   <si>
+    <t>BR-226;CE-371;Avenida Joaquim Dantas Pinheiro;Rua João Alfredo Pinheiro;Avenida Vereador Acácio Nascimento Silva;OSM-tertiary;Rua José Gomes Pinheiro</t>
+  </si>
+  <si>
     <t>CE-153;BR-122;CE-153;CE-368;BR-122;CE-266;CE-371;Avenida Governador Manoel de Castro Filho;Avenida do Contorno;Rua José Guerra;Estrada para Jaguaribe;Rua Maria do Socorro Oliveira;Avenida Ex Combatente Cricerio Pinheiro Maia;OSM-tertiary</t>
   </si>
   <si>
@@ -1282,9 +1312,6 @@
     <t>BR-226;BR-226;CE-060;OSM-tertiary</t>
   </si>
   <si>
-    <t>BR-226;OSM-tertiary;BR-226;CE-060</t>
-  </si>
-  <si>
     <t>BR-226;CE-060;CE-060;CE-363;CE-363;OSM-tertiary;CE-363;CE-168;Rua Ana Soares Pedrosa 2;CE-168;Rua Antônio Marcos Pereira;Rua Professor Osorino Mendes;Rua José Paulino de Sousa;BR-226;CE-168</t>
   </si>
   <si>
@@ -1297,7 +1324,7 @@
     <t>BR-226;Rodovia Presidente Juscelino Kubitschek;BR-020;CE-587;OSM-tertiary;Rua Antônio Marcos Pereira;Rua Professor Osorino Mendes;Rua José Paulino de Sousa</t>
   </si>
   <si>
-    <t>BR-404;CE-189;Rua Quintino Cunha;Travessa Menino Jesus;Rua Lima Campos;Rua Agamenon Machado;Rua Coronel Lúcio;Rua Francisco Sá;Rua Bento Coutinho;Avenida Sargento Hermínio;Rua Antônio Catuanda;Rua Alexandre Bonfim;BR-404;CE-187</t>
+    <t>BR-404;CE-187;Rua Alexandre Bonfim;Rua Antônio Catuanda;Avenida Sargento Hermínio;Rua Francisco Sá;Rua Bento Coutinho;Rua Coronel Lúcio;Rua Agamenon Machado;Rua Lima Campos;Travessa Menino Jesus;Rua Quintino Cunha;BR-404;CE-189</t>
   </si>
   <si>
     <t>BR-404;CE-189;Rua Joaquim Lopes de Araújo;Rua Gentil Falção;OSM-tertiary;Rua Menezes PImentel;Rua Padre Juvêncio;Rua Firmino Rosa;CE-447</t>
@@ -1327,15 +1354,12 @@
     <t>BR-403;CE-183;CE-253;CE-321;BR-222</t>
   </si>
   <si>
-    <t>BR-404;CE-189;Rua Quintino Cunha;Travessa Menino Jesus;Rua Lima Campos;Rua Agamenon Machado;Rua Anizio Frota;Rua Menezes PImentel;OSM-tertiary;Rua Gentil Falção;Rua Hanneman Magalhães</t>
+    <t>BR-404;CE-189;BR-404;CE-187;Rua Alexandre Bonfim;Rua Antônio Catuanda;Avenida Sargento Hermínio;Rua Francisco Sá;Rua Bento Coutinho;Rua Coronel Lúcio;Rua Agamenon Machado;Rua Anizio Frota;Rua Menezes PImentel;OSM-tertiary;Rua Gentil Falção;Rua Hanneman Magalhães</t>
   </si>
   <si>
     <t>Avenida Senador Fernandes Távora;Avenida Moacir Lima Feijão;OSM-secondary;Avenida Monsenhor Aloísio Pinto;Rua Coronel Antônio Rodrigues Magalhães</t>
   </si>
   <si>
-    <t>BR-222;CE-362;CE-253;OSM-tertiary;CE-179;BR-222;BR-403;OSM-trunk_link</t>
-  </si>
-  <si>
     <t>Rua Othon de Alencar;Rua Oriano Mendes;Rua Doutor Carlito Pompeu;Avenida Monsenhor Aloísio Pinto;OSM-secondary;Avenida Moacir Lima Feijão;Avenida Senador Fernandes Távora</t>
   </si>
   <si>
@@ -1348,15 +1372,15 @@
     <t>BR-222;BR-403;Avenida Senador Fernandes Távora;Rua Caetano Figueiredo;Rua 07;Rua Raimundo Rodrigues;Avenida Julys Alisson Soares Balrreira;BR-403;CE-178;OSM-trunk_link</t>
   </si>
   <si>
+    <t>Avenida Senador José Ermírio de Moraes;CE-417;Avenida Ministro César Cals;Rua Manoel Marinho de Andrade;Rua Manuel Marinho de Andrade</t>
+  </si>
+  <si>
+    <t>BR-403;CE-085;BR-403;CE-216;BR-402;CE-179;Avenida Tenente Albano;OSM-primary;OSM-trunk;CE-085</t>
+  </si>
+  <si>
     <t>BR-020;CE-251;Estrada para Caraussanga;Rodovia Raimundo Pessoa de Araújo;OSM-trunk_link</t>
   </si>
   <si>
-    <t>Avenida Senador José Ermírio de Moraes;CE-417;Avenida Ministro César Cals;Rua Manoel Marinho de Andrade;Rua Manuel Marinho de Andrade</t>
-  </si>
-  <si>
-    <t>BR-403;CE-085;BR-403;CE-216;BR-402;CE-179;Avenida Tenente Albano;OSM-primary;OSM-trunk;CE-085</t>
-  </si>
-  <si>
     <t>BR-020;OSM-trunk_link;OSM-tertiary;Estrada do Corrente - Ipu - Tucunduba;CE-065;Avenida Doutor Stênio Gomes;Rua Chico Anísio;Rua Capitão Jeová Colares;Rua Doutor Argeu Braga Herbster;CE-251;Estrada para Caraussanga</t>
   </si>
   <si>
@@ -1390,6 +1414,9 @@
     <t>CE-189;BR-404;CE-189;Avenida Raimundo Evaristo;Rua Aleixo Vieira;OSM-tertiary;Rua Saturnino Abreu Memória;CE-265;Rua Luís Vieira Torres;Rua João Almeida Filho</t>
   </si>
   <si>
+    <t>BR-403;CE-085;CE-085;OSM-trunk;OSM-primary;Avenida Tenente Albano;CE-179;CE-216;BR-402;BR-403</t>
+  </si>
+  <si>
     <t>BR-122;Avenida Jesus Maria e José;Rua Tenente Cravo;Rua Ader Ferreira Araújo;Avenida Plácido Castelo;CE-060;OSM-primary_link;CE-356;BR-122;CE-359;OSM-primary</t>
   </si>
   <si>
@@ -1432,7 +1459,10 @@
     <t>BR-116;Rua Antônio Saraiva;Avenida Raimundo Simplicio de Carvalho</t>
   </si>
   <si>
-    <t>BR-116;CE-138;OSM-tertiary</t>
+    <t>BR-116;OSM-tertiary;CE-138</t>
+  </si>
+  <si>
+    <t>BR-116</t>
   </si>
   <si>
     <t>BR-116;CE-251;CE-251;Rodovia Deputado Paulino Rocha;Avenida Jorge Cavalcate;Avenida Lidia Alves Cavalcante;OSM-secondary;BR-116;CE-350;BR-116;CE-350;CE-251;OSM-trunk_link</t>
@@ -1456,12 +1486,12 @@
     <t>BR-116;CE-138;CE-356;BR-122;CE-359;OSM-tertiary</t>
   </si>
   <si>
+    <t>BR-122;BR-122;CE-359;CE-356;CE-060;OSM-primary_link;Avenida Plácido Castelo;Rua Ader Ferreira Araújo;Rua Tenente Cravo;Avenida Jesus Maria e José;OSM-primary</t>
+  </si>
+  <si>
     <t>BR-122;OSM-primary_link;OSM-primary;Avenida Jesus Maria e José;Rua Tenente Cravo;Rua Ader Ferreira Araújo;Avenida Plácido Castelo;CE-060;CE-356;BR-122;CE-359</t>
   </si>
   <si>
-    <t>BR-122;BR-122;CE-359;CE-356;CE-060;OSM-primary_link;Avenida Plácido Castelo;Rua Ader Ferreira Araújo;Rua Tenente Cravo;Avenida Jesus Maria e José;OSM-primary</t>
-  </si>
-  <si>
     <t>BR-122;Avenida Presidente Vargas;CE-060;CE-265;Rua Tenente Cravo</t>
   </si>
   <si>
@@ -1480,15 +1510,12 @@
     <t>BR-122;OSM-primary;OSM-primary_link;BR-122;CE-359;CE-356;CE-060;Avenida Plácido Castelo;Rua Ader Ferreira Araújo;Rua Tenente Cravo;Avenida Jesus Maria e José</t>
   </si>
   <si>
-    <t>BR-116;CE-371;Rua Miguel Rodrigues Santiago;CE-123;OSM-primary;BR-304;OSM-trunk</t>
+    <t>BR-116;OSM-trunk;BR-304;OSM-primary;CE-123;CE-371;Rua Miguel Rodrigues Santiago</t>
   </si>
   <si>
     <t>BR-116;CE-371;CE-356;OSM-tertiary;Rua Pedro Alves de Sousa;Rua Francisco Bandeira de Melo;CE-522;OSM-trunk_link</t>
   </si>
   <si>
-    <t>BR-116;OSM-trunk;BR-304;OSM-primary;CE-123;CE-371;Rua Miguel Rodrigues Santiago</t>
-  </si>
-  <si>
     <t>BR-116;OSM-trunk_link;CE-522;Rua Francisco Bandeira de Melo;Rua Pedro Alves de Sousa;OSM-tertiary;CE-371;CE-356</t>
   </si>
   <si>
@@ -1516,7 +1543,7 @@
     <t>CE-216;BR-402;OSM-primary_link;BR-402;BR-403;CE-178;BR-402;BR-403;BR-403;BR-403;CE-354;CE-178;BR-403;CE-178;CE-354;CE-179</t>
   </si>
   <si>
-    <t>BR-437;CE-266;BR-437;CE-358;CE-358;CE-358;CE-377;OSM-tertiary;CE-265;CE-266</t>
+    <t>BR-437;CE-266;OSM-tertiary;CE-266;CE-265;CE-358;CE-377;CE-358;BR-437;CE-358</t>
   </si>
   <si>
     <t>BR-116;CE-269;Avenida Vereador Sobrinho;OSM-secondary;CE-546;OSM-secondary_link;CE-371;Avenida Governador Manoel de Castro Filho;Avenida do Contorno;Rua José Guerra;Estrada para Jaguaribe;CE-368;BR-226;CE-368;CE-275;Avenida Almir Tavora;Avenida Virgílio Távora;Rua Maria Cecilia Diogenes;Rua Sigefredo Diógenes</t>
@@ -1528,7 +1555,7 @@
     <t>BR-116;Avenida Oito de Novembro;Avenida Oito de novembro;Rua Sigefredo Diógenes;Rua Raimundo Albani</t>
   </si>
   <si>
-    <t>BR-404;CE-189;CE-189;Rua João Almeida Filho;Rua Luís Vieira Torres;CE-265;Rua Saturnino Abreu Memória;OSM-tertiary;Rua Aleixo Vieira;Avenida Raimundo Evaristo</t>
+    <t>BR-404;CE-189;Avenida Raimundo Evaristo;Rua Aleixo Vieira;OSM-tertiary;Rua Saturnino Abreu Memória;CE-265;Rua Luís Vieira Torres;Rua João Almeida Filho;CE-189</t>
   </si>
   <si>
     <t>CE-168;BR-402;CE-354;Rua José de Alencar</t>
@@ -1543,6 +1570,12 @@
     <t>BR-304;Avenida Olímpica;OSM-secondary;CE-371;Avenida João Barbosa Lima;CE-123;OSM-primary</t>
   </si>
   <si>
+    <t>BR-222;OSM-tertiary;Estrada Garrote;Estrada do Garrote;CE-085;Rua José Holanda Nogueira;Avenida Cruzeiro do Sul</t>
+  </si>
+  <si>
+    <t>OSM-trunk_link;BR-222;CE-156;CE-085;OSM-tertiary;Estrada da Área da Petrobrás;CE-348</t>
+  </si>
+  <si>
     <t>BR-222;OSM-tertiary;Estrada Garrote;CE-348</t>
   </si>
   <si>
@@ -1558,9 +1591,6 @@
     <t>grafo_desconexo</t>
   </si>
   <si>
-    <t>sem_interseccao</t>
-  </si>
-  <si>
     <t>BR-020;CE-363;CE-363;CE-168;OSM-tertiary;CE-060;CE-363;CE-060;BR-226;BR-226;CE-168;Rodovia Presidente Juscelino Kubitschek</t>
   </si>
   <si>
@@ -1573,9 +1603,6 @@
     <t>BR-020;OSM-trunk_link;CE-065;Rua Doutor Argeu Braga Herbster;Rua Capitão Jeová Colares;Rua Chico Anísio;Avenida Doutor Stênio Gomes;CE-455;CE-354</t>
   </si>
   <si>
-    <t>BR-020;CE-279;Estrada Santa Rita;CE-277;BR-020;CE-277</t>
-  </si>
-  <si>
     <t>BR-222;OSM-trunk_link;BR-222;BR-403;Avenida Senador Fernandes Távora;Avenida Maria da Conceição Pontes de Azevedo;Estrada das Marrecas;Avenida Prefeito José Euclides Ferreira Gomes Júnior;CE-417;BR-403;CE-178;CE-240;CE-176;OSM-tertiary;Avenida Linha Francisco Marques;Rodovia Doutor José Euclides Ferreira Gomes Júnior</t>
   </si>
   <si>
@@ -1585,15 +1612,6 @@
     <t>BR-222;CE-313;CE-240;CE-364;CE-321</t>
   </si>
   <si>
-    <t>BR-222;OSM-secondary;Rua Capitão Joaquim Francisco;CE-581</t>
-  </si>
-  <si>
-    <t>BR-402;CE-354;OSM-tertiary;OSM-secondary</t>
-  </si>
-  <si>
-    <t>BR-402;CE-354;CE-333;CE-139;URB-030;Rua Coronel João Antônio;Rua João Galdino Vasconcelos;Rua Marcolino Evangelista;Avenida Artur Rodrigues Vasconcelos;CE-354;URB-010;OSM-secondary</t>
-  </si>
-  <si>
     <t>BR-402;CE-243;CE-354;CE-243;URB-040;CE-243;Rua Farmacêutico José Rodrigues;CE-243;URB-060;CE-243;URB-164;Avenida Júlio Pinheiro Bastos;OSM-tertiary;BR-222</t>
   </si>
   <si>
@@ -1609,15 +1627,6 @@
     <t>BR-222;CE-243;Rua Major Joaquim Alexandre;Rua Major João Ribeiro;Rua Manoel Luiz da Rocha;Rua Fausto Pinheiro;CE-243;URB-060;URB-178;URB-070;CE-333;CE-168;BR-402;CE-354;Rua Dom Aureliano Matos;Avenida Anastácio Braga;BR-402;CE-240;CE-240;OSM-primary;Rua Dezinho Teixeira;OSM-tertiary;Rua Luiz Matias;Avenida Lindolfo Braga;CE-176;Rodovia Doutor José Euclides Ferreira Gomes Júnior;OSM-trunk_link;Avenida Paulo Bastos</t>
   </si>
   <si>
-    <t>BR-222;OSM-tertiary;CE-243;Rua Francisco José de Oliveira;Rua Antônio Braga;CE-168</t>
-  </si>
-  <si>
-    <t>BR-222;OSM-tertiary</t>
-  </si>
-  <si>
-    <t>BR-222;CE-168;OSM-tertiary</t>
-  </si>
-  <si>
     <t>BR-222;Avenida Cruzeiro do Sul;Rua Coronel Correia;Rua Barão de Ibiapaba;Avenida da Integração;Avenida de Contorno Leste;Rodovia Raimundo Pessoa de Araújo;BR-020</t>
   </si>
   <si>
@@ -1669,9 +1678,6 @@
     <t>BR-226;CE-363;BR-226;CE-060;CE-060;CE-060;CE-363;CE-166;OSM-secondary;Avenida José Chagas Filho;OSM-tertiary;Rua Antônio Pessoa de Carvalho;Rua Franco Magalhães;Rua Antônio Soares;Rua Sisgismundo Rodrigues</t>
   </si>
   <si>
-    <t>BR-226;CE-371;Avenida Joaquim Dantas Pinheiro;Rua João Alfredo Pinheiro;Avenida Vereador Acácio Nascimento Silva;OSM-tertiary;Rua José Gomes Pinheiro</t>
-  </si>
-  <si>
     <t>BR-226;CE-166;CE-060;CE-363</t>
   </si>
   <si>
@@ -1687,12 +1693,6 @@
     <t>BR-226;CE-168;Rua Balbina Vieira Almeida;CE-266;Rua Antônio Domingues;Rua Antônio Rocha Bezerra;BR-020;Rodovia Presidente Juscelino Kubitschek</t>
   </si>
   <si>
-    <t>BR-404;CE-187;Rua Alexandre Bonfim;Rua Antônio Catuanda;Avenida Sargento Hermínio;Rua Francisco Sá;Rua Bento Coutinho;Rua Coronel Lúcio;Rua Agamenon Machado;Rua Lima Campos;Travessa Menino Jesus;Rua Quintino Cunha;BR-404;CE-189</t>
-  </si>
-  <si>
-    <t>BR-404;CE-189;BR-404;CE-187;Rua Alexandre Bonfim;Rua Antônio Catuanda;Avenida Sargento Hermínio;Rua Francisco Sá;Rua Bento Coutinho;Rua Coronel Lúcio;Rua Agamenon Machado;Rua Anizio Frota;Rua Menezes PImentel;OSM-tertiary;Rua Gentil Falção;Rua Hanneman Magalhães</t>
-  </si>
-  <si>
     <t>BR-222;BR-403;Avenida Senador Fernandes Távora;Avenida Maria da Conceição Pontes de Azevedo;Estrada das Marrecas;Avenida Prefeito José Euclides Ferreira Gomes Júnior;CE-417;BR-403;CE-178;CE-240;CE-176;OSM-tertiary;Avenida Linha Francisco Marques;Rodovia Doutor José Euclides Ferreira Gomes Júnior;OSM-trunk_link;BR-222</t>
   </si>
   <si>
@@ -1702,9 +1702,6 @@
     <t>CE-216;BR-402;CE-179;Avenida Tenente Albano;OSM-primary;OSM-trunk;CE-085;BR-403;CE-085;BR-403</t>
   </si>
   <si>
-    <t>BR-403;CE-085;CE-085;OSM-trunk;OSM-primary;Avenida Tenente Albano;CE-179;CE-216;BR-402;BR-403</t>
-  </si>
-  <si>
     <t>BR-122;Avenida Jesus Maria e José;Rua Tenente Cravo;Rua Ader Ferreira Araújo;Avenida Plácido Castelo;CE-060;OSM-primary_link;CE-464;OSM-tertiary;BR-122;CE-359;OSM-primary</t>
   </si>
   <si>
@@ -1723,9 +1720,6 @@
     <t>BR-116;Avenida Raimundo Simplicio de Carvalho;OSM-secondary;OSM-trunk_link;Rua Cônego Eduardo Araripe;Rua José Abel de Azevedo;Rua Coronel Cícero de Nogueira Queiroz;CE-253;CE-040;CE-497</t>
   </si>
   <si>
-    <t>BR-116</t>
-  </si>
-  <si>
     <t>BR-116;CE-251;BR-116;OSM-trunk_link;BR-020;OSM-tertiary;Avenida Dionísio Leonel Alencar;Rua Raimundo Rodrigues Serpa;Rua Otávio de Matos;Avenida do Gavião;CE-251;Rodovia Deputado Paulino Rocha;Avenida Jorge Cavalcate;Avenida Lidia Alves Cavalcante;OSM-secondary;BR-116;CE-350;BR-116;CE-350;CE-251</t>
   </si>
   <si>
@@ -1754,15 +1748,6 @@
   </si>
   <si>
     <t>CE-216;BR-402;BR-403;BR-403;CE-085;CE-085;OSM-trunk;OSM-primary;Avenida Tenente Albano;CE-179</t>
-  </si>
-  <si>
-    <t>BR-404;CE-189;Avenida Raimundo Evaristo;Rua Aleixo Vieira;OSM-tertiary;Rua Saturnino Abreu Memória;CE-265;Rua Luís Vieira Torres;Rua João Almeida Filho;CE-189</t>
-  </si>
-  <si>
-    <t>BR-222;OSM-tertiary;Estrada Garrote;Estrada do Garrote;CE-085;Rua José Holanda Nogueira;Avenida Cruzeiro do Sul</t>
-  </si>
-  <si>
-    <t>OSM-trunk_link;BR-222;CE-156;CE-085;OSM-tertiary;Estrada da Área da Petrobrás;CE-348</t>
   </si>
 </sst>
 </file>
@@ -2166,7 +2151,7 @@
         <v>320</v>
       </c>
       <c r="D2">
-        <v>8.730399999999999</v>
+        <v>8.673400000000001</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -2198,7 +2183,7 @@
         <v>320</v>
       </c>
       <c r="D3">
-        <v>55.1941</v>
+        <v>55.1376</v>
       </c>
       <c r="E3">
         <v>13</v>
@@ -2230,7 +2215,7 @@
         <v>320</v>
       </c>
       <c r="D4">
-        <v>55.1957</v>
+        <v>55.1352</v>
       </c>
       <c r="E4">
         <v>13</v>
@@ -2262,7 +2247,7 @@
         <v>320</v>
       </c>
       <c r="D5">
-        <v>1.6249</v>
+        <v>1.5193</v>
       </c>
       <c r="E5">
         <v>3</v>
@@ -2376,7 +2361,7 @@
         <v>13</v>
       </c>
       <c r="J8" t="s">
-        <v>515</v>
+        <v>525</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -2390,7 +2375,7 @@
         <v>320</v>
       </c>
       <c r="D9">
-        <v>170.3849</v>
+        <v>170.3238</v>
       </c>
       <c r="E9">
         <v>6</v>
@@ -2408,7 +2393,7 @@
         <v>13</v>
       </c>
       <c r="J9" t="s">
-        <v>515</v>
+        <v>525</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -2422,7 +2407,7 @@
         <v>320</v>
       </c>
       <c r="D10">
-        <v>170.3578</v>
+        <v>170.3158</v>
       </c>
       <c r="E10">
         <v>6</v>
@@ -2440,7 +2425,7 @@
         <v>13</v>
       </c>
       <c r="J10" t="s">
-        <v>516</v>
+        <v>526</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -2454,7 +2439,7 @@
         <v>320</v>
       </c>
       <c r="D11">
-        <v>170.3595</v>
+        <v>170.3167</v>
       </c>
       <c r="E11">
         <v>6</v>
@@ -2472,7 +2457,7 @@
         <v>13</v>
       </c>
       <c r="J11" t="s">
-        <v>515</v>
+        <v>525</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -2486,7 +2471,7 @@
         <v>320</v>
       </c>
       <c r="D12">
-        <v>170.3854</v>
+        <v>170.3253</v>
       </c>
       <c r="E12">
         <v>6</v>
@@ -2504,7 +2489,7 @@
         <v>13</v>
       </c>
       <c r="J12" t="s">
-        <v>515</v>
+        <v>525</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -2536,7 +2521,7 @@
         <v>13</v>
       </c>
       <c r="J13" t="s">
-        <v>515</v>
+        <v>525</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -2646,7 +2631,7 @@
         <v>320</v>
       </c>
       <c r="D17">
-        <v>125.6405</v>
+        <v>125.6002</v>
       </c>
       <c r="E17">
         <v>10</v>
@@ -2728,7 +2713,7 @@
         <v>14</v>
       </c>
       <c r="J19" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="20" spans="1:10">
@@ -2742,7 +2727,7 @@
         <v>320</v>
       </c>
       <c r="D20">
-        <v>5.025</v>
+        <v>4.9809</v>
       </c>
       <c r="E20">
         <v>8</v>
@@ -2774,7 +2759,7 @@
         <v>320</v>
       </c>
       <c r="D21">
-        <v>143.2026</v>
+        <v>143.1682</v>
       </c>
       <c r="E21">
         <v>11</v>
@@ -2806,7 +2791,7 @@
         <v>320</v>
       </c>
       <c r="D22">
-        <v>143.2509</v>
+        <v>143.2094</v>
       </c>
       <c r="E22">
         <v>11</v>
@@ -2838,7 +2823,7 @@
         <v>320</v>
       </c>
       <c r="D23">
-        <v>108.882</v>
+        <v>108.8464</v>
       </c>
       <c r="E23">
         <v>9</v>
@@ -2888,7 +2873,7 @@
         <v>15</v>
       </c>
       <c r="J24" t="s">
-        <v>517</v>
+        <v>527</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -2902,7 +2887,7 @@
         <v>320</v>
       </c>
       <c r="D25">
-        <v>87.00449999999999</v>
+        <v>86.9014</v>
       </c>
       <c r="E25">
         <v>9</v>
@@ -2920,7 +2905,7 @@
         <v>15</v>
       </c>
       <c r="J25" t="s">
-        <v>517</v>
+        <v>527</v>
       </c>
     </row>
     <row r="26" spans="1:10">
@@ -2934,7 +2919,7 @@
         <v>320</v>
       </c>
       <c r="D26">
-        <v>87.0142</v>
+        <v>86.9479</v>
       </c>
       <c r="E26">
         <v>9</v>
@@ -2952,7 +2937,7 @@
         <v>15</v>
       </c>
       <c r="J26" t="s">
-        <v>517</v>
+        <v>527</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -2966,7 +2951,7 @@
         <v>320</v>
       </c>
       <c r="D27">
-        <v>24.325</v>
+        <v>24.1986</v>
       </c>
       <c r="E27">
         <v>8</v>
@@ -2984,7 +2969,7 @@
         <v>15</v>
       </c>
       <c r="J27" t="s">
-        <v>518</v>
+        <v>528</v>
       </c>
     </row>
     <row r="28" spans="1:10">
@@ -2998,7 +2983,7 @@
         <v>320</v>
       </c>
       <c r="D28">
-        <v>87.01819999999999</v>
+        <v>86.95699999999999</v>
       </c>
       <c r="E28">
         <v>9</v>
@@ -3016,7 +3001,7 @@
         <v>15</v>
       </c>
       <c r="J28" t="s">
-        <v>517</v>
+        <v>527</v>
       </c>
     </row>
     <row r="29" spans="1:10">
@@ -3039,7 +3024,7 @@
         <v>338</v>
       </c>
       <c r="G29" t="s">
-        <v>513</v>
+        <v>524</v>
       </c>
       <c r="H29">
         <v>0</v>
@@ -3091,13 +3076,13 @@
         <v>320</v>
       </c>
       <c r="D31">
-        <v>70.2038</v>
+        <v>70.18300000000001</v>
       </c>
       <c r="E31">
         <v>6</v>
       </c>
       <c r="F31" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="G31" t="s">
         <v>320</v>
@@ -3109,7 +3094,7 @@
         <v>6</v>
       </c>
       <c r="J31" t="s">
-        <v>519</v>
+        <v>340</v>
       </c>
     </row>
     <row r="32" spans="1:10">
@@ -3123,7 +3108,7 @@
         <v>320</v>
       </c>
       <c r="D32">
-        <v>19.7507</v>
+        <v>19.7065</v>
       </c>
       <c r="E32">
         <v>4</v>
@@ -3155,7 +3140,7 @@
         <v>320</v>
       </c>
       <c r="D33">
-        <v>170.386</v>
+        <v>170.326</v>
       </c>
       <c r="E33">
         <v>6</v>
@@ -3173,7 +3158,7 @@
         <v>13</v>
       </c>
       <c r="J33" t="s">
-        <v>515</v>
+        <v>525</v>
       </c>
     </row>
     <row r="34" spans="1:10">
@@ -3187,7 +3172,7 @@
         <v>320</v>
       </c>
       <c r="D34">
-        <v>170.3593</v>
+        <v>170.3167</v>
       </c>
       <c r="E34">
         <v>6</v>
@@ -3205,7 +3190,7 @@
         <v>13</v>
       </c>
       <c r="J34" t="s">
-        <v>515</v>
+        <v>525</v>
       </c>
     </row>
     <row r="35" spans="1:10">
@@ -3219,13 +3204,13 @@
         <v>320</v>
       </c>
       <c r="D35">
-        <v>125.6751</v>
+        <v>125.5995</v>
       </c>
       <c r="E35">
         <v>10</v>
       </c>
       <c r="F35" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="G35" t="s">
         <v>320</v>
@@ -3257,7 +3242,7 @@
         <v>10</v>
       </c>
       <c r="F36" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="G36" t="s">
         <v>320</v>
@@ -3269,7 +3254,7 @@
         <v>10</v>
       </c>
       <c r="J36" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="37" spans="1:10">
@@ -3283,13 +3268,13 @@
         <v>320</v>
       </c>
       <c r="D37">
-        <v>104.4023</v>
+        <v>104.3267</v>
       </c>
       <c r="E37">
         <v>10</v>
       </c>
       <c r="F37" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="G37" t="s">
         <v>320</v>
@@ -3301,7 +3286,7 @@
         <v>10</v>
       </c>
       <c r="J37" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="38" spans="1:10">
@@ -3321,7 +3306,7 @@
         <v>14</v>
       </c>
       <c r="F38" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="G38" t="s">
         <v>320</v>
@@ -3333,7 +3318,7 @@
         <v>14</v>
       </c>
       <c r="J38" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="39" spans="1:10">
@@ -3353,7 +3338,7 @@
         <v>14</v>
       </c>
       <c r="F39" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="G39" t="s">
         <v>320</v>
@@ -3365,7 +3350,7 @@
         <v>14</v>
       </c>
       <c r="J39" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="40" spans="1:10">
@@ -3385,7 +3370,7 @@
         <v>10</v>
       </c>
       <c r="F40" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="G40" t="s">
         <v>320</v>
@@ -3397,7 +3382,7 @@
         <v>10</v>
       </c>
       <c r="J40" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="41" spans="1:10">
@@ -3411,13 +3396,13 @@
         <v>320</v>
       </c>
       <c r="D41">
-        <v>121.7097</v>
+        <v>121.6511</v>
       </c>
       <c r="E41">
         <v>9</v>
       </c>
       <c r="F41" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="G41" t="s">
         <v>320</v>
@@ -3429,7 +3414,7 @@
         <v>9</v>
       </c>
       <c r="J41" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="42" spans="1:10">
@@ -3475,7 +3460,7 @@
         <v>320</v>
       </c>
       <c r="D43">
-        <v>143.2684</v>
+        <v>143.2077</v>
       </c>
       <c r="E43">
         <v>11</v>
@@ -3507,13 +3492,13 @@
         <v>320</v>
       </c>
       <c r="D44">
-        <v>3.1487</v>
+        <v>3.1255</v>
       </c>
       <c r="E44">
         <v>6</v>
       </c>
       <c r="F44" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G44" t="s">
         <v>320</v>
@@ -3525,7 +3510,7 @@
         <v>6</v>
       </c>
       <c r="J44" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="45" spans="1:10">
@@ -3539,13 +3524,13 @@
         <v>320</v>
       </c>
       <c r="D45">
-        <v>87.033</v>
+        <v>86.9367</v>
       </c>
       <c r="E45">
         <v>9</v>
       </c>
       <c r="F45" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="G45" t="s">
         <v>320</v>
@@ -3557,7 +3542,7 @@
         <v>15</v>
       </c>
       <c r="J45" t="s">
-        <v>518</v>
+        <v>528</v>
       </c>
     </row>
     <row r="46" spans="1:10">
@@ -3571,13 +3556,13 @@
         <v>320</v>
       </c>
       <c r="D46">
-        <v>92.5437</v>
+        <v>92.52290000000001</v>
       </c>
       <c r="E46">
         <v>6</v>
       </c>
       <c r="F46" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="G46" t="s">
         <v>320</v>
@@ -3589,7 +3574,7 @@
         <v>6</v>
       </c>
       <c r="J46" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="47" spans="1:10">
@@ -3603,13 +3588,13 @@
         <v>320</v>
       </c>
       <c r="D47">
-        <v>41.9056</v>
+        <v>41.8094</v>
       </c>
       <c r="E47">
         <v>7</v>
       </c>
       <c r="F47" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="G47" t="s">
         <v>320</v>
@@ -3621,7 +3606,7 @@
         <v>7</v>
       </c>
       <c r="J47" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="48" spans="1:10">
@@ -3635,13 +3620,13 @@
         <v>320</v>
       </c>
       <c r="D48">
-        <v>41.8893</v>
+        <v>41.8463</v>
       </c>
       <c r="E48">
         <v>7</v>
       </c>
       <c r="F48" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="G48" t="s">
         <v>320</v>
@@ -3653,7 +3638,7 @@
         <v>7</v>
       </c>
       <c r="J48" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="49" spans="1:10">
@@ -3667,13 +3652,13 @@
         <v>320</v>
       </c>
       <c r="D49">
-        <v>61.5258</v>
+        <v>61.4642</v>
       </c>
       <c r="E49">
         <v>9</v>
       </c>
       <c r="F49" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="G49" t="s">
         <v>320</v>
@@ -3685,7 +3670,7 @@
         <v>18</v>
       </c>
       <c r="J49" t="s">
-        <v>520</v>
+        <v>529</v>
       </c>
     </row>
     <row r="50" spans="1:10">
@@ -3699,13 +3684,13 @@
         <v>320</v>
       </c>
       <c r="D50">
-        <v>41.8902</v>
+        <v>41.8471</v>
       </c>
       <c r="E50">
         <v>7</v>
       </c>
       <c r="F50" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="G50" t="s">
         <v>320</v>
@@ -3717,7 +3702,7 @@
         <v>7</v>
       </c>
       <c r="J50" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="51" spans="1:10">
@@ -3731,13 +3716,13 @@
         <v>320</v>
       </c>
       <c r="D51">
-        <v>75.9105</v>
+        <v>75.8668</v>
       </c>
       <c r="E51">
         <v>5</v>
       </c>
       <c r="F51" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="G51" t="s">
         <v>320</v>
@@ -3749,7 +3734,7 @@
         <v>5</v>
       </c>
       <c r="J51" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="52" spans="1:10">
@@ -3763,13 +3748,13 @@
         <v>320</v>
       </c>
       <c r="D52">
-        <v>88.12860000000001</v>
+        <v>88.0609</v>
       </c>
       <c r="E52">
         <v>15</v>
       </c>
       <c r="F52" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="G52" t="s">
         <v>320</v>
@@ -3781,7 +3766,7 @@
         <v>7</v>
       </c>
       <c r="J52" t="s">
-        <v>521</v>
+        <v>530</v>
       </c>
     </row>
     <row r="53" spans="1:10">
@@ -3795,13 +3780,13 @@
         <v>320</v>
       </c>
       <c r="D53">
-        <v>88.13</v>
+        <v>88.0367</v>
       </c>
       <c r="E53">
         <v>15</v>
       </c>
       <c r="F53" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="G53" t="s">
         <v>320</v>
@@ -3813,7 +3798,7 @@
         <v>7</v>
       </c>
       <c r="J53" t="s">
-        <v>522</v>
+        <v>531</v>
       </c>
     </row>
     <row r="54" spans="1:10">
@@ -3827,13 +3812,13 @@
         <v>320</v>
       </c>
       <c r="D54">
-        <v>88.14960000000001</v>
+        <v>88.0535</v>
       </c>
       <c r="E54">
         <v>15</v>
       </c>
       <c r="F54" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="G54" t="s">
         <v>320</v>
@@ -3845,7 +3830,7 @@
         <v>7</v>
       </c>
       <c r="J54" t="s">
-        <v>522</v>
+        <v>531</v>
       </c>
     </row>
     <row r="55" spans="1:10">
@@ -3859,13 +3844,13 @@
         <v>320</v>
       </c>
       <c r="D55">
-        <v>88.1456</v>
+        <v>88.1024</v>
       </c>
       <c r="E55">
         <v>15</v>
       </c>
       <c r="F55" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="G55" t="s">
         <v>320</v>
@@ -3877,7 +3862,7 @@
         <v>7</v>
       </c>
       <c r="J55" t="s">
-        <v>522</v>
+        <v>531</v>
       </c>
     </row>
     <row r="56" spans="1:10">
@@ -3891,13 +3876,13 @@
         <v>320</v>
       </c>
       <c r="D56">
-        <v>88.10429999999999</v>
+        <v>88.0585</v>
       </c>
       <c r="E56">
         <v>15</v>
       </c>
       <c r="F56" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="G56" t="s">
         <v>320</v>
@@ -3909,7 +3894,7 @@
         <v>7</v>
       </c>
       <c r="J56" t="s">
-        <v>522</v>
+        <v>531</v>
       </c>
     </row>
     <row r="57" spans="1:10">
@@ -3923,13 +3908,13 @@
         <v>320</v>
       </c>
       <c r="D57">
-        <v>3.0155</v>
+        <v>2.9432</v>
       </c>
       <c r="E57">
         <v>5</v>
       </c>
       <c r="F57" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="G57" t="s">
         <v>320</v>
@@ -3941,7 +3926,7 @@
         <v>5</v>
       </c>
       <c r="J57" t="s">
-        <v>523</v>
+        <v>356</v>
       </c>
     </row>
     <row r="58" spans="1:10">
@@ -3955,13 +3940,13 @@
         <v>320</v>
       </c>
       <c r="D58">
-        <v>88.1073</v>
+        <v>88.0851</v>
       </c>
       <c r="E58">
         <v>15</v>
       </c>
       <c r="F58" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="G58" t="s">
         <v>320</v>
@@ -3973,7 +3958,7 @@
         <v>7</v>
       </c>
       <c r="J58" t="s">
-        <v>522</v>
+        <v>531</v>
       </c>
     </row>
     <row r="59" spans="1:10">
@@ -3987,13 +3972,13 @@
         <v>320</v>
       </c>
       <c r="D59">
-        <v>3.0782</v>
+        <v>3.0298</v>
       </c>
       <c r="E59">
         <v>4</v>
       </c>
       <c r="F59" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="G59" t="s">
         <v>320</v>
@@ -4005,7 +3990,7 @@
         <v>4</v>
       </c>
       <c r="J59" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="60" spans="1:10">
@@ -4019,13 +4004,13 @@
         <v>320</v>
       </c>
       <c r="D60">
-        <v>88.6948</v>
+        <v>88.626</v>
       </c>
       <c r="E60">
         <v>12</v>
       </c>
       <c r="F60" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="G60" t="s">
         <v>320</v>
@@ -4037,7 +4022,7 @@
         <v>7</v>
       </c>
       <c r="J60" t="s">
-        <v>521</v>
+        <v>530</v>
       </c>
     </row>
     <row r="61" spans="1:10">
@@ -4051,13 +4036,13 @@
         <v>320</v>
       </c>
       <c r="D61">
-        <v>88.6995</v>
+        <v>88.6563</v>
       </c>
       <c r="E61">
         <v>12</v>
       </c>
       <c r="F61" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="G61" t="s">
         <v>320</v>
@@ -4069,7 +4054,7 @@
         <v>7</v>
       </c>
       <c r="J61" t="s">
-        <v>521</v>
+        <v>530</v>
       </c>
     </row>
     <row r="62" spans="1:10">
@@ -4083,13 +4068,13 @@
         <v>320</v>
       </c>
       <c r="D62">
-        <v>61.5294</v>
+        <v>61.4713</v>
       </c>
       <c r="E62">
         <v>9</v>
       </c>
       <c r="F62" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="G62" t="s">
         <v>320</v>
@@ -4101,7 +4086,7 @@
         <v>18</v>
       </c>
       <c r="J62" t="s">
-        <v>520</v>
+        <v>529</v>
       </c>
     </row>
     <row r="63" spans="1:10">
@@ -4115,13 +4100,13 @@
         <v>320</v>
       </c>
       <c r="D63">
-        <v>88.69459999999999</v>
+        <v>88.62520000000001</v>
       </c>
       <c r="E63">
         <v>12</v>
       </c>
       <c r="F63" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="G63" t="s">
         <v>320</v>
@@ -4133,7 +4118,7 @@
         <v>7</v>
       </c>
       <c r="J63" t="s">
-        <v>522</v>
+        <v>531</v>
       </c>
     </row>
     <row r="64" spans="1:10">
@@ -4147,13 +4132,13 @@
         <v>320</v>
       </c>
       <c r="D64">
-        <v>88.6927</v>
+        <v>88.62269999999999</v>
       </c>
       <c r="E64">
         <v>12</v>
       </c>
       <c r="F64" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="G64" t="s">
         <v>320</v>
@@ -4165,7 +4150,7 @@
         <v>7</v>
       </c>
       <c r="J64" t="s">
-        <v>522</v>
+        <v>531</v>
       </c>
     </row>
     <row r="65" spans="1:10">
@@ -4179,13 +4164,13 @@
         <v>320</v>
       </c>
       <c r="D65">
-        <v>88.7176</v>
+        <v>88.6198</v>
       </c>
       <c r="E65">
         <v>12</v>
       </c>
       <c r="F65" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="G65" t="s">
         <v>320</v>
@@ -4197,7 +4182,7 @@
         <v>7</v>
       </c>
       <c r="J65" t="s">
-        <v>521</v>
+        <v>530</v>
       </c>
     </row>
     <row r="66" spans="1:10">
@@ -4249,7 +4234,7 @@
         <v>5</v>
       </c>
       <c r="F67" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="G67" t="s">
         <v>320</v>
@@ -4261,7 +4246,7 @@
         <v>5</v>
       </c>
       <c r="J67" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
     </row>
     <row r="68" spans="1:10">
@@ -4281,7 +4266,7 @@
         <v>5</v>
       </c>
       <c r="F68" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="G68" t="s">
         <v>320</v>
@@ -4293,7 +4278,7 @@
         <v>5</v>
       </c>
       <c r="J68" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
     </row>
     <row r="69" spans="1:10">
@@ -4313,7 +4298,7 @@
         <v>5</v>
       </c>
       <c r="F69" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="G69" t="s">
         <v>320</v>
@@ -4325,7 +4310,7 @@
         <v>5</v>
       </c>
       <c r="J69" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
     </row>
     <row r="70" spans="1:10">
@@ -4345,7 +4330,7 @@
         <v>3</v>
       </c>
       <c r="F70" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="G70" t="s">
         <v>320</v>
@@ -4357,7 +4342,7 @@
         <v>3</v>
       </c>
       <c r="J70" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
     </row>
     <row r="71" spans="1:10">
@@ -4377,7 +4362,7 @@
         <v>3</v>
       </c>
       <c r="F71" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="G71" t="s">
         <v>320</v>
@@ -4389,7 +4374,7 @@
         <v>3</v>
       </c>
       <c r="J71" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
     </row>
     <row r="72" spans="1:10">
@@ -4409,7 +4394,7 @@
         <v>3</v>
       </c>
       <c r="F72" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="G72" t="s">
         <v>320</v>
@@ -4421,7 +4406,7 @@
         <v>3</v>
       </c>
       <c r="J72" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
     </row>
     <row r="73" spans="1:10">
@@ -4441,7 +4426,7 @@
         <v>3</v>
       </c>
       <c r="F73" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="G73" t="s">
         <v>320</v>
@@ -4453,7 +4438,7 @@
         <v>3</v>
       </c>
       <c r="J73" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
     </row>
     <row r="74" spans="1:10">
@@ -4467,13 +4452,13 @@
         <v>320</v>
       </c>
       <c r="D74">
-        <v>39.9469</v>
+        <v>39.9028</v>
       </c>
       <c r="E74">
         <v>8</v>
       </c>
       <c r="F74" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="G74" t="s">
         <v>320</v>
@@ -4485,7 +4470,7 @@
         <v>8</v>
       </c>
       <c r="J74" t="s">
-        <v>381</v>
+        <v>364</v>
       </c>
     </row>
     <row r="75" spans="1:10">
@@ -4499,13 +4484,13 @@
         <v>320</v>
       </c>
       <c r="D75">
-        <v>31.5874</v>
+        <v>31.5535</v>
       </c>
       <c r="E75">
         <v>10</v>
       </c>
       <c r="F75" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="G75" t="s">
         <v>320</v>
@@ -4517,7 +4502,7 @@
         <v>10</v>
       </c>
       <c r="J75" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
     </row>
     <row r="76" spans="1:10">
@@ -4531,13 +4516,13 @@
         <v>320</v>
       </c>
       <c r="D76">
-        <v>51.7718</v>
+        <v>51.6731</v>
       </c>
       <c r="E76">
         <v>11</v>
       </c>
       <c r="F76" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="G76" t="s">
         <v>320</v>
@@ -4549,7 +4534,7 @@
         <v>11</v>
       </c>
       <c r="J76" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="77" spans="1:10">
@@ -4563,13 +4548,13 @@
         <v>320</v>
       </c>
       <c r="D77">
-        <v>18.9438</v>
+        <v>18.8986</v>
       </c>
       <c r="E77">
         <v>4</v>
       </c>
       <c r="F77" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="G77" t="s">
         <v>320</v>
@@ -4581,7 +4566,7 @@
         <v>4</v>
       </c>
       <c r="J77" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="78" spans="1:10">
@@ -4595,13 +4580,13 @@
         <v>320</v>
       </c>
       <c r="D78">
-        <v>10.1746</v>
+        <v>10.0192</v>
       </c>
       <c r="E78">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F78" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="G78" t="s">
         <v>320</v>
@@ -4613,7 +4598,7 @@
         <v>3</v>
       </c>
       <c r="J78" t="s">
-        <v>524</v>
+        <v>368</v>
       </c>
     </row>
     <row r="79" spans="1:10">
@@ -4627,13 +4612,13 @@
         <v>320</v>
       </c>
       <c r="D79">
-        <v>30.2342</v>
+        <v>30.1661</v>
       </c>
       <c r="E79">
         <v>12</v>
       </c>
       <c r="F79" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="G79" t="s">
         <v>320</v>
@@ -4645,7 +4630,7 @@
         <v>12</v>
       </c>
       <c r="J79" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
     </row>
     <row r="80" spans="1:10">
@@ -4659,13 +4644,13 @@
         <v>320</v>
       </c>
       <c r="D80">
-        <v>30.2344</v>
+        <v>30.1662</v>
       </c>
       <c r="E80">
         <v>12</v>
       </c>
       <c r="F80" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="G80" t="s">
         <v>320</v>
@@ -4677,7 +4662,7 @@
         <v>12</v>
       </c>
       <c r="J80" t="s">
-        <v>525</v>
+        <v>370</v>
       </c>
     </row>
     <row r="81" spans="1:10">
@@ -4691,13 +4676,13 @@
         <v>320</v>
       </c>
       <c r="D81">
-        <v>11.9535</v>
+        <v>11.9032</v>
       </c>
       <c r="E81">
         <v>7</v>
       </c>
       <c r="F81" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="G81" t="s">
         <v>320</v>
@@ -4709,7 +4694,7 @@
         <v>7</v>
       </c>
       <c r="J81" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
     </row>
     <row r="82" spans="1:10">
@@ -4723,13 +4708,13 @@
         <v>320</v>
       </c>
       <c r="D82">
-        <v>30.1518</v>
+        <v>30.0915</v>
       </c>
       <c r="E82">
         <v>14</v>
       </c>
       <c r="F82" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="G82" t="s">
         <v>320</v>
@@ -4741,7 +4726,7 @@
         <v>13</v>
       </c>
       <c r="J82" t="s">
-        <v>526</v>
+        <v>532</v>
       </c>
     </row>
     <row r="83" spans="1:10">
@@ -4755,13 +4740,13 @@
         <v>320</v>
       </c>
       <c r="D83">
-        <v>92.52200000000001</v>
+        <v>92.4782</v>
       </c>
       <c r="E83">
         <v>7</v>
       </c>
       <c r="F83" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="G83" t="s">
         <v>320</v>
@@ -4773,7 +4758,7 @@
         <v>7</v>
       </c>
       <c r="J83" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
     </row>
     <row r="84" spans="1:10">
@@ -4793,7 +4778,7 @@
         <v>4</v>
       </c>
       <c r="F84" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="G84" t="s">
         <v>320</v>
@@ -4805,7 +4790,7 @@
         <v>4</v>
       </c>
       <c r="J84" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
     </row>
     <row r="85" spans="1:10">
@@ -4819,13 +4804,13 @@
         <v>320</v>
       </c>
       <c r="D85">
-        <v>103.0834</v>
+        <v>103.0271</v>
       </c>
       <c r="E85">
         <v>15</v>
       </c>
       <c r="F85" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="G85" t="s">
         <v>320</v>
@@ -4837,7 +4822,7 @@
         <v>36</v>
       </c>
       <c r="J85" t="s">
-        <v>527</v>
+        <v>533</v>
       </c>
     </row>
     <row r="86" spans="1:10">
@@ -4851,13 +4836,13 @@
         <v>320</v>
       </c>
       <c r="D86">
-        <v>103.0339</v>
+        <v>102.9923</v>
       </c>
       <c r="E86">
         <v>15</v>
       </c>
       <c r="F86" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="G86" t="s">
         <v>320</v>
@@ -4869,7 +4854,7 @@
         <v>36</v>
       </c>
       <c r="J86" t="s">
-        <v>528</v>
+        <v>534</v>
       </c>
     </row>
     <row r="87" spans="1:10">
@@ -4883,13 +4868,13 @@
         <v>320</v>
       </c>
       <c r="D87">
-        <v>103.0853</v>
+        <v>103.0295</v>
       </c>
       <c r="E87">
         <v>15</v>
       </c>
       <c r="F87" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="G87" t="s">
         <v>320</v>
@@ -4901,7 +4886,7 @@
         <v>36</v>
       </c>
       <c r="J87" t="s">
-        <v>528</v>
+        <v>534</v>
       </c>
     </row>
     <row r="88" spans="1:10">
@@ -4915,13 +4900,13 @@
         <v>320</v>
       </c>
       <c r="D88">
-        <v>114.0156</v>
+        <v>113.9412</v>
       </c>
       <c r="E88">
         <v>24</v>
       </c>
       <c r="F88" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="G88" t="s">
         <v>320</v>
@@ -4933,7 +4918,7 @@
         <v>36</v>
       </c>
       <c r="J88" t="s">
-        <v>528</v>
+        <v>534</v>
       </c>
     </row>
     <row r="89" spans="1:10">
@@ -4947,13 +4932,13 @@
         <v>320</v>
       </c>
       <c r="D89">
-        <v>114.0093</v>
+        <v>113.9684</v>
       </c>
       <c r="E89">
         <v>24</v>
       </c>
       <c r="F89" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="G89" t="s">
         <v>320</v>
@@ -4965,7 +4950,7 @@
         <v>36</v>
       </c>
       <c r="J89" t="s">
-        <v>529</v>
+        <v>535</v>
       </c>
     </row>
     <row r="90" spans="1:10">
@@ -4979,13 +4964,13 @@
         <v>320</v>
       </c>
       <c r="D90">
-        <v>114.0305</v>
+        <v>113.9694</v>
       </c>
       <c r="E90">
         <v>24</v>
       </c>
       <c r="F90" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="G90" t="s">
         <v>320</v>
@@ -4997,7 +4982,7 @@
         <v>36</v>
       </c>
       <c r="J90" t="s">
-        <v>530</v>
+        <v>536</v>
       </c>
     </row>
     <row r="91" spans="1:10">
@@ -5011,13 +4996,13 @@
         <v>320</v>
       </c>
       <c r="D91">
-        <v>114.035</v>
+        <v>113.9519</v>
       </c>
       <c r="E91">
         <v>24</v>
       </c>
       <c r="F91" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="G91" t="s">
         <v>320</v>
@@ -5029,7 +5014,7 @@
         <v>36</v>
       </c>
       <c r="J91" t="s">
-        <v>530</v>
+        <v>536</v>
       </c>
     </row>
     <row r="92" spans="1:10">
@@ -5043,13 +5028,13 @@
         <v>320</v>
       </c>
       <c r="D92">
-        <v>29.9158</v>
+        <v>29.8736</v>
       </c>
       <c r="E92">
         <v>8</v>
       </c>
       <c r="F92" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="G92" t="s">
         <v>320</v>
@@ -5061,7 +5046,7 @@
         <v>8</v>
       </c>
       <c r="J92" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
     </row>
     <row r="93" spans="1:10">
@@ -5075,13 +5060,13 @@
         <v>320</v>
       </c>
       <c r="D93">
-        <v>29.9591</v>
+        <v>29.8153</v>
       </c>
       <c r="E93">
         <v>8</v>
       </c>
       <c r="F93" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="G93" t="s">
         <v>320</v>
@@ -5093,7 +5078,7 @@
         <v>8</v>
       </c>
       <c r="J93" t="s">
-        <v>531</v>
+        <v>381</v>
       </c>
     </row>
     <row r="94" spans="1:10">
@@ -5107,13 +5092,13 @@
         <v>320</v>
       </c>
       <c r="D94">
-        <v>8.8017</v>
+        <v>20.0395</v>
       </c>
       <c r="E94">
         <v>3</v>
       </c>
       <c r="F94" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="G94" t="s">
         <v>320</v>
@@ -5125,7 +5110,7 @@
         <v>3</v>
       </c>
       <c r="J94" t="s">
-        <v>532</v>
+        <v>382</v>
       </c>
     </row>
     <row r="95" spans="1:10">
@@ -5139,13 +5124,13 @@
         <v>320</v>
       </c>
       <c r="D95">
-        <v>8.8405</v>
+        <v>8.7599</v>
       </c>
       <c r="E95">
         <v>4</v>
       </c>
       <c r="F95" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="G95" t="s">
         <v>320</v>
@@ -5157,7 +5142,7 @@
         <v>4</v>
       </c>
       <c r="J95" t="s">
-        <v>533</v>
+        <v>383</v>
       </c>
     </row>
     <row r="96" spans="1:10">
@@ -5171,13 +5156,13 @@
         <v>320</v>
       </c>
       <c r="D96">
-        <v>23.7935</v>
+        <v>23.7583</v>
       </c>
       <c r="E96">
         <v>10</v>
       </c>
       <c r="F96" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="G96" t="s">
         <v>320</v>
@@ -5189,7 +5174,7 @@
         <v>10</v>
       </c>
       <c r="J96" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
     </row>
     <row r="97" spans="1:10">
@@ -5209,7 +5194,7 @@
         <v>9</v>
       </c>
       <c r="F97" t="s">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="G97" t="s">
         <v>320</v>
@@ -5221,7 +5206,7 @@
         <v>9</v>
       </c>
       <c r="J97" t="s">
-        <v>379</v>
+        <v>385</v>
       </c>
     </row>
     <row r="98" spans="1:10">
@@ -5241,7 +5226,7 @@
         <v>9</v>
       </c>
       <c r="F98" t="s">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="G98" t="s">
         <v>320</v>
@@ -5253,7 +5238,7 @@
         <v>9</v>
       </c>
       <c r="J98" t="s">
-        <v>379</v>
+        <v>385</v>
       </c>
     </row>
     <row r="99" spans="1:10">
@@ -5273,7 +5258,7 @@
         <v>5</v>
       </c>
       <c r="F99" t="s">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="G99" t="s">
         <v>320</v>
@@ -5285,7 +5270,7 @@
         <v>5</v>
       </c>
       <c r="J99" t="s">
-        <v>380</v>
+        <v>386</v>
       </c>
     </row>
     <row r="100" spans="1:10">
@@ -5305,7 +5290,7 @@
         <v>8</v>
       </c>
       <c r="F100" t="s">
-        <v>361</v>
+        <v>387</v>
       </c>
       <c r="G100" t="s">
         <v>320</v>
@@ -5317,7 +5302,7 @@
         <v>8</v>
       </c>
       <c r="J100" t="s">
-        <v>361</v>
+        <v>387</v>
       </c>
     </row>
     <row r="101" spans="1:10">
@@ -5331,13 +5316,13 @@
         <v>320</v>
       </c>
       <c r="D101">
-        <v>39.9585</v>
+        <v>39.9188</v>
       </c>
       <c r="E101">
         <v>8</v>
       </c>
       <c r="F101" t="s">
-        <v>381</v>
+        <v>364</v>
       </c>
       <c r="G101" t="s">
         <v>320</v>
@@ -5349,7 +5334,7 @@
         <v>8</v>
       </c>
       <c r="J101" t="s">
-        <v>381</v>
+        <v>364</v>
       </c>
     </row>
     <row r="102" spans="1:10">
@@ -5369,7 +5354,7 @@
         <v>8</v>
       </c>
       <c r="F102" t="s">
-        <v>381</v>
+        <v>364</v>
       </c>
       <c r="G102" t="s">
         <v>320</v>
@@ -5381,7 +5366,7 @@
         <v>8</v>
       </c>
       <c r="J102" t="s">
-        <v>381</v>
+        <v>364</v>
       </c>
     </row>
     <row r="103" spans="1:10">
@@ -5395,7 +5380,7 @@
         <v>320</v>
       </c>
       <c r="D103">
-        <v>55.1279</v>
+        <v>55.0342</v>
       </c>
       <c r="E103">
         <v>13</v>
@@ -5404,13 +5389,16 @@
         <v>322</v>
       </c>
       <c r="G103" t="s">
-        <v>514</v>
+        <v>320</v>
       </c>
       <c r="H103">
-        <v>0</v>
+        <v>55.0342</v>
       </c>
       <c r="I103">
-        <v>0</v>
+        <v>13</v>
+      </c>
+      <c r="J103" t="s">
+        <v>322</v>
       </c>
     </row>
     <row r="104" spans="1:10">
@@ -5424,13 +5412,13 @@
         <v>320</v>
       </c>
       <c r="D104">
-        <v>57.9341</v>
+        <v>57.8687</v>
       </c>
       <c r="E104">
         <v>12</v>
       </c>
       <c r="F104" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="G104" t="s">
         <v>320</v>
@@ -5442,7 +5430,7 @@
         <v>10</v>
       </c>
       <c r="J104" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
     </row>
     <row r="105" spans="1:10">
@@ -5462,7 +5450,7 @@
         <v>9</v>
       </c>
       <c r="F105" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="G105" t="s">
         <v>320</v>
@@ -5474,7 +5462,7 @@
         <v>10</v>
       </c>
       <c r="J105" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
     </row>
     <row r="106" spans="1:10">
@@ -5488,13 +5476,13 @@
         <v>320</v>
       </c>
       <c r="D106">
-        <v>68.58329999999999</v>
+        <v>68.5228</v>
       </c>
       <c r="E106">
         <v>9</v>
       </c>
       <c r="F106" t="s">
-        <v>383</v>
+        <v>390</v>
       </c>
       <c r="G106" t="s">
         <v>320</v>
@@ -5506,7 +5494,7 @@
         <v>10</v>
       </c>
       <c r="J106" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
     </row>
     <row r="107" spans="1:10">
@@ -5520,13 +5508,13 @@
         <v>320</v>
       </c>
       <c r="D107">
-        <v>68.58920000000001</v>
+        <v>68.50620000000001</v>
       </c>
       <c r="E107">
         <v>9</v>
       </c>
       <c r="F107" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="G107" t="s">
         <v>320</v>
@@ -5538,7 +5526,7 @@
         <v>10</v>
       </c>
       <c r="J107" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
     </row>
     <row r="108" spans="1:10">
@@ -5552,7 +5540,7 @@
         <v>320</v>
       </c>
       <c r="D108">
-        <v>8.742100000000001</v>
+        <v>8.6838</v>
       </c>
       <c r="E108">
         <v>1</v>
@@ -5584,13 +5572,13 @@
         <v>320</v>
       </c>
       <c r="D109">
-        <v>30.1835</v>
+        <v>30.122</v>
       </c>
       <c r="E109">
         <v>14</v>
       </c>
       <c r="F109" t="s">
-        <v>384</v>
+        <v>391</v>
       </c>
       <c r="G109" t="s">
         <v>320</v>
@@ -5602,7 +5590,7 @@
         <v>13</v>
       </c>
       <c r="J109" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="110" spans="1:10">
@@ -5616,13 +5604,13 @@
         <v>320</v>
       </c>
       <c r="D110">
-        <v>49.5705</v>
+        <v>49.52</v>
       </c>
       <c r="E110">
         <v>18</v>
       </c>
       <c r="F110" t="s">
-        <v>385</v>
+        <v>392</v>
       </c>
       <c r="G110" t="s">
         <v>320</v>
@@ -5634,7 +5622,7 @@
         <v>13</v>
       </c>
       <c r="J110" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
     </row>
     <row r="111" spans="1:10">
@@ -5648,13 +5636,13 @@
         <v>320</v>
       </c>
       <c r="D111">
-        <v>49.5932</v>
+        <v>49.5404</v>
       </c>
       <c r="E111">
         <v>18</v>
       </c>
       <c r="F111" t="s">
-        <v>386</v>
+        <v>393</v>
       </c>
       <c r="G111" t="s">
         <v>320</v>
@@ -5666,7 +5654,7 @@
         <v>13</v>
       </c>
       <c r="J111" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="112" spans="1:10">
@@ -5680,13 +5668,13 @@
         <v>320</v>
       </c>
       <c r="D112">
-        <v>49.5924</v>
+        <v>49.5112</v>
       </c>
       <c r="E112">
         <v>18</v>
       </c>
       <c r="F112" t="s">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="G112" t="s">
         <v>320</v>
@@ -5698,7 +5686,7 @@
         <v>13</v>
       </c>
       <c r="J112" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="113" spans="1:10">
@@ -5718,7 +5706,7 @@
         <v>7</v>
       </c>
       <c r="F113" t="s">
-        <v>387</v>
+        <v>394</v>
       </c>
       <c r="G113" t="s">
         <v>320</v>
@@ -5730,7 +5718,7 @@
         <v>20</v>
       </c>
       <c r="J113" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
     </row>
     <row r="114" spans="1:10">
@@ -5744,13 +5732,13 @@
         <v>320</v>
       </c>
       <c r="D114">
-        <v>34.832</v>
+        <v>34.807</v>
       </c>
       <c r="E114">
         <v>6</v>
       </c>
       <c r="F114" t="s">
-        <v>388</v>
+        <v>395</v>
       </c>
       <c r="G114" t="s">
         <v>320</v>
@@ -5762,7 +5750,7 @@
         <v>6</v>
       </c>
       <c r="J114" t="s">
-        <v>388</v>
+        <v>395</v>
       </c>
     </row>
     <row r="115" spans="1:10">
@@ -5776,13 +5764,13 @@
         <v>320</v>
       </c>
       <c r="D115">
-        <v>45.69</v>
+        <v>45.6699</v>
       </c>
       <c r="E115">
         <v>6</v>
       </c>
       <c r="F115" t="s">
-        <v>389</v>
+        <v>396</v>
       </c>
       <c r="G115" t="s">
         <v>320</v>
@@ -5794,7 +5782,7 @@
         <v>6</v>
       </c>
       <c r="J115" t="s">
-        <v>389</v>
+        <v>396</v>
       </c>
     </row>
     <row r="116" spans="1:10">
@@ -5814,7 +5802,7 @@
         <v>21</v>
       </c>
       <c r="F116" t="s">
-        <v>390</v>
+        <v>397</v>
       </c>
       <c r="G116" t="s">
         <v>320</v>
@@ -5826,7 +5814,7 @@
         <v>36</v>
       </c>
       <c r="J116" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
     </row>
     <row r="117" spans="1:10">
@@ -5846,7 +5834,7 @@
         <v>8</v>
       </c>
       <c r="F117" t="s">
-        <v>391</v>
+        <v>398</v>
       </c>
       <c r="G117" t="s">
         <v>320</v>
@@ -5858,7 +5846,7 @@
         <v>8</v>
       </c>
       <c r="J117" t="s">
-        <v>391</v>
+        <v>398</v>
       </c>
     </row>
     <row r="118" spans="1:10">
@@ -5872,13 +5860,13 @@
         <v>320</v>
       </c>
       <c r="D118">
-        <v>36.7005</v>
+        <v>36.6483</v>
       </c>
       <c r="E118">
         <v>6</v>
       </c>
       <c r="F118" t="s">
-        <v>392</v>
+        <v>399</v>
       </c>
       <c r="G118" t="s">
         <v>320</v>
@@ -5890,7 +5878,7 @@
         <v>6</v>
       </c>
       <c r="J118" t="s">
-        <v>392</v>
+        <v>399</v>
       </c>
     </row>
     <row r="119" spans="1:10">
@@ -5910,7 +5898,7 @@
         <v>21</v>
       </c>
       <c r="F119" t="s">
-        <v>393</v>
+        <v>400</v>
       </c>
       <c r="G119" t="s">
         <v>320</v>
@@ -5922,7 +5910,7 @@
         <v>36</v>
       </c>
       <c r="J119" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
     </row>
     <row r="120" spans="1:10">
@@ -5936,13 +5924,13 @@
         <v>320</v>
       </c>
       <c r="D120">
-        <v>45.6997</v>
+        <v>45.654</v>
       </c>
       <c r="E120">
         <v>6</v>
       </c>
       <c r="F120" t="s">
-        <v>394</v>
+        <v>401</v>
       </c>
       <c r="G120" t="s">
         <v>320</v>
@@ -5954,7 +5942,7 @@
         <v>6</v>
       </c>
       <c r="J120" t="s">
-        <v>394</v>
+        <v>401</v>
       </c>
     </row>
     <row r="121" spans="1:10">
@@ -5968,13 +5956,13 @@
         <v>320</v>
       </c>
       <c r="D121">
-        <v>83.3663</v>
+        <v>83.3107</v>
       </c>
       <c r="E121">
         <v>10</v>
       </c>
       <c r="F121" t="s">
-        <v>395</v>
+        <v>402</v>
       </c>
       <c r="G121" t="s">
         <v>320</v>
@@ -5986,7 +5974,7 @@
         <v>36</v>
       </c>
       <c r="J121" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
     </row>
     <row r="122" spans="1:10">
@@ -6000,13 +5988,13 @@
         <v>320</v>
       </c>
       <c r="D122">
-        <v>96.2229</v>
+        <v>96.17610000000001</v>
       </c>
       <c r="E122">
         <v>10</v>
       </c>
       <c r="F122" t="s">
-        <v>396</v>
+        <v>403</v>
       </c>
       <c r="G122" t="s">
         <v>320</v>
@@ -6018,7 +6006,7 @@
         <v>36</v>
       </c>
       <c r="J122" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
     </row>
     <row r="123" spans="1:10">
@@ -6032,13 +6020,13 @@
         <v>320</v>
       </c>
       <c r="D123">
-        <v>170.4821</v>
+        <v>170.4151</v>
       </c>
       <c r="E123">
         <v>21</v>
       </c>
       <c r="F123" t="s">
-        <v>397</v>
+        <v>404</v>
       </c>
       <c r="G123" t="s">
         <v>320</v>
@@ -6050,7 +6038,7 @@
         <v>36</v>
       </c>
       <c r="J123" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
     </row>
     <row r="124" spans="1:10">
@@ -6064,13 +6052,13 @@
         <v>320</v>
       </c>
       <c r="D124">
-        <v>96.2461</v>
+        <v>96.2115</v>
       </c>
       <c r="E124">
         <v>10</v>
       </c>
       <c r="F124" t="s">
-        <v>396</v>
+        <v>405</v>
       </c>
       <c r="G124" t="s">
         <v>320</v>
@@ -6082,7 +6070,7 @@
         <v>36</v>
       </c>
       <c r="J124" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
     </row>
     <row r="125" spans="1:10">
@@ -6102,7 +6090,7 @@
         <v>21</v>
       </c>
       <c r="F125" t="s">
-        <v>398</v>
+        <v>406</v>
       </c>
       <c r="G125" t="s">
         <v>320</v>
@@ -6114,7 +6102,7 @@
         <v>36</v>
       </c>
       <c r="J125" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
     </row>
     <row r="126" spans="1:10">
@@ -6128,13 +6116,13 @@
         <v>320</v>
       </c>
       <c r="D126">
-        <v>170.4899</v>
+        <v>170.4288</v>
       </c>
       <c r="E126">
         <v>21</v>
       </c>
       <c r="F126" t="s">
-        <v>393</v>
+        <v>400</v>
       </c>
       <c r="G126" t="s">
         <v>320</v>
@@ -6146,7 +6134,7 @@
         <v>36</v>
       </c>
       <c r="J126" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
     </row>
     <row r="127" spans="1:10">
@@ -6166,7 +6154,7 @@
         <v>13</v>
       </c>
       <c r="F127" t="s">
-        <v>399</v>
+        <v>407</v>
       </c>
       <c r="G127" t="s">
         <v>320</v>
@@ -6178,7 +6166,7 @@
         <v>37</v>
       </c>
       <c r="J127" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
     </row>
     <row r="128" spans="1:10">
@@ -6192,13 +6180,13 @@
         <v>320</v>
       </c>
       <c r="D128">
-        <v>73.50839999999999</v>
+        <v>73.4555</v>
       </c>
       <c r="E128">
         <v>11</v>
       </c>
       <c r="F128" t="s">
-        <v>400</v>
+        <v>408</v>
       </c>
       <c r="G128" t="s">
         <v>320</v>
@@ -6210,7 +6198,7 @@
         <v>11</v>
       </c>
       <c r="J128" t="s">
-        <v>400</v>
+        <v>408</v>
       </c>
     </row>
     <row r="129" spans="1:10">
@@ -6230,7 +6218,7 @@
         <v>10</v>
       </c>
       <c r="F129" t="s">
-        <v>401</v>
+        <v>409</v>
       </c>
       <c r="G129" t="s">
         <v>320</v>
@@ -6242,7 +6230,7 @@
         <v>10</v>
       </c>
       <c r="J129" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
     </row>
     <row r="130" spans="1:10">
@@ -6256,16 +6244,16 @@
         <v>320</v>
       </c>
       <c r="D130">
-        <v>25.5463</v>
+        <v>25.4822</v>
       </c>
       <c r="E130">
         <v>6</v>
       </c>
       <c r="F130" t="s">
-        <v>402</v>
+        <v>410</v>
       </c>
       <c r="G130" t="s">
-        <v>513</v>
+        <v>524</v>
       </c>
       <c r="H130">
         <v>0</v>
@@ -6285,13 +6273,13 @@
         <v>320</v>
       </c>
       <c r="D131">
-        <v>96.2805</v>
+        <v>96.223</v>
       </c>
       <c r="E131">
         <v>10</v>
       </c>
       <c r="F131" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="G131" t="s">
         <v>320</v>
@@ -6303,7 +6291,7 @@
         <v>10</v>
       </c>
       <c r="J131" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
     </row>
     <row r="132" spans="1:10">
@@ -6323,7 +6311,7 @@
         <v>4</v>
       </c>
       <c r="F132" t="s">
-        <v>403</v>
+        <v>412</v>
       </c>
       <c r="G132" t="s">
         <v>320</v>
@@ -6335,7 +6323,7 @@
         <v>4</v>
       </c>
       <c r="J132" t="s">
-        <v>403</v>
+        <v>412</v>
       </c>
     </row>
     <row r="133" spans="1:10">
@@ -6349,13 +6337,13 @@
         <v>320</v>
       </c>
       <c r="D133">
-        <v>32.2342</v>
+        <v>32.1775</v>
       </c>
       <c r="E133">
         <v>5</v>
       </c>
       <c r="F133" t="s">
-        <v>404</v>
+        <v>413</v>
       </c>
       <c r="G133" t="s">
         <v>320</v>
@@ -6367,7 +6355,7 @@
         <v>5</v>
       </c>
       <c r="J133" t="s">
-        <v>404</v>
+        <v>413</v>
       </c>
     </row>
     <row r="134" spans="1:10">
@@ -6381,13 +6369,13 @@
         <v>320</v>
       </c>
       <c r="D134">
-        <v>84.79600000000001</v>
+        <v>84.7504</v>
       </c>
       <c r="E134">
         <v>9</v>
       </c>
       <c r="F134" t="s">
-        <v>405</v>
+        <v>414</v>
       </c>
       <c r="G134" t="s">
         <v>320</v>
@@ -6399,7 +6387,7 @@
         <v>15</v>
       </c>
       <c r="J134" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
     </row>
     <row r="135" spans="1:10">
@@ -6413,16 +6401,16 @@
         <v>320</v>
       </c>
       <c r="D135">
-        <v>107.5217</v>
+        <v>107.4643</v>
       </c>
       <c r="E135">
         <v>9</v>
       </c>
       <c r="F135" t="s">
-        <v>406</v>
+        <v>415</v>
       </c>
       <c r="G135" t="s">
-        <v>513</v>
+        <v>524</v>
       </c>
       <c r="H135">
         <v>0</v>
@@ -6442,16 +6430,16 @@
         <v>320</v>
       </c>
       <c r="D136">
-        <v>34.8128</v>
+        <v>34.7508</v>
       </c>
       <c r="E136">
         <v>6</v>
       </c>
       <c r="F136" t="s">
-        <v>407</v>
+        <v>416</v>
       </c>
       <c r="G136" t="s">
-        <v>513</v>
+        <v>524</v>
       </c>
       <c r="H136">
         <v>0</v>
@@ -6471,16 +6459,16 @@
         <v>320</v>
       </c>
       <c r="D137">
-        <v>112.419</v>
+        <v>112.3259</v>
       </c>
       <c r="E137">
         <v>11</v>
       </c>
       <c r="F137" t="s">
-        <v>408</v>
+        <v>417</v>
       </c>
       <c r="G137" t="s">
-        <v>513</v>
+        <v>524</v>
       </c>
       <c r="H137">
         <v>0</v>
@@ -6500,13 +6488,13 @@
         <v>320</v>
       </c>
       <c r="D138">
-        <v>84.8591</v>
+        <v>84.79300000000001</v>
       </c>
       <c r="E138">
         <v>9</v>
       </c>
       <c r="F138" t="s">
-        <v>405</v>
+        <v>414</v>
       </c>
       <c r="G138" t="s">
         <v>320</v>
@@ -6518,7 +6506,7 @@
         <v>15</v>
       </c>
       <c r="J138" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
     </row>
     <row r="139" spans="1:10">
@@ -6538,7 +6526,7 @@
         <v>24</v>
       </c>
       <c r="F139" t="s">
-        <v>409</v>
+        <v>418</v>
       </c>
       <c r="G139" t="s">
         <v>320</v>
@@ -6550,7 +6538,7 @@
         <v>24</v>
       </c>
       <c r="J139" t="s">
-        <v>409</v>
+        <v>418</v>
       </c>
     </row>
     <row r="140" spans="1:10">
@@ -6570,10 +6558,10 @@
         <v>17</v>
       </c>
       <c r="F140" t="s">
-        <v>410</v>
+        <v>419</v>
       </c>
       <c r="G140" t="s">
-        <v>513</v>
+        <v>524</v>
       </c>
       <c r="H140">
         <v>0</v>
@@ -6593,13 +6581,13 @@
         <v>320</v>
       </c>
       <c r="D141">
-        <v>43.8109</v>
+        <v>43.7611</v>
       </c>
       <c r="E141">
         <v>9</v>
       </c>
       <c r="F141" t="s">
-        <v>411</v>
+        <v>420</v>
       </c>
       <c r="G141" t="s">
         <v>320</v>
@@ -6611,7 +6599,7 @@
         <v>9</v>
       </c>
       <c r="J141" t="s">
-        <v>411</v>
+        <v>420</v>
       </c>
     </row>
     <row r="142" spans="1:10">
@@ -6631,7 +6619,7 @@
         <v>8</v>
       </c>
       <c r="F142" t="s">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="G142" t="s">
         <v>320</v>
@@ -6643,7 +6631,7 @@
         <v>18</v>
       </c>
       <c r="J142" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
     </row>
     <row r="143" spans="1:10">
@@ -6657,13 +6645,13 @@
         <v>320</v>
       </c>
       <c r="D143">
-        <v>43.761</v>
+        <v>43.6817</v>
       </c>
       <c r="E143">
         <v>9</v>
       </c>
       <c r="F143" t="s">
-        <v>411</v>
+        <v>422</v>
       </c>
       <c r="G143" t="s">
         <v>320</v>
@@ -6675,7 +6663,7 @@
         <v>9</v>
       </c>
       <c r="J143" t="s">
-        <v>551</v>
+        <v>422</v>
       </c>
     </row>
     <row r="144" spans="1:10">
@@ -6695,7 +6683,7 @@
         <v>13</v>
       </c>
       <c r="F144" t="s">
-        <v>413</v>
+        <v>423</v>
       </c>
       <c r="G144" t="s">
         <v>320</v>
@@ -6707,7 +6695,7 @@
         <v>13</v>
       </c>
       <c r="J144" t="s">
-        <v>413</v>
+        <v>423</v>
       </c>
     </row>
     <row r="145" spans="1:10">
@@ -6727,10 +6715,10 @@
         <v>17</v>
       </c>
       <c r="F145" t="s">
-        <v>414</v>
+        <v>424</v>
       </c>
       <c r="G145" t="s">
-        <v>513</v>
+        <v>524</v>
       </c>
       <c r="H145">
         <v>0</v>
@@ -6750,13 +6738,13 @@
         <v>320</v>
       </c>
       <c r="D146">
-        <v>3.9554</v>
+        <v>3.9152</v>
       </c>
       <c r="E146">
         <v>9</v>
       </c>
       <c r="F146" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="G146" t="s">
         <v>320</v>
@@ -6768,7 +6756,7 @@
         <v>6</v>
       </c>
       <c r="J146" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
     </row>
     <row r="147" spans="1:10">
@@ -6788,10 +6776,10 @@
         <v>17</v>
       </c>
       <c r="F147" t="s">
-        <v>410</v>
+        <v>419</v>
       </c>
       <c r="G147" t="s">
-        <v>513</v>
+        <v>524</v>
       </c>
       <c r="H147">
         <v>0</v>
@@ -6811,13 +6799,13 @@
         <v>320</v>
       </c>
       <c r="D148">
-        <v>88.5299</v>
+        <v>88.4845</v>
       </c>
       <c r="E148">
         <v>5</v>
       </c>
       <c r="F148" t="s">
-        <v>416</v>
+        <v>426</v>
       </c>
       <c r="G148" t="s">
         <v>320</v>
@@ -6829,7 +6817,7 @@
         <v>6</v>
       </c>
       <c r="J148" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
     </row>
     <row r="149" spans="1:10">
@@ -6843,13 +6831,13 @@
         <v>320</v>
       </c>
       <c r="D149">
-        <v>15.6474</v>
+        <v>15.6031</v>
       </c>
       <c r="E149">
         <v>3</v>
       </c>
       <c r="F149" t="s">
-        <v>417</v>
+        <v>427</v>
       </c>
       <c r="G149" t="s">
         <v>320</v>
@@ -6861,7 +6849,7 @@
         <v>3</v>
       </c>
       <c r="J149" t="s">
-        <v>417</v>
+        <v>427</v>
       </c>
     </row>
     <row r="150" spans="1:10">
@@ -6875,13 +6863,13 @@
         <v>320</v>
       </c>
       <c r="D150">
-        <v>88.5296</v>
+        <v>88.4586</v>
       </c>
       <c r="E150">
         <v>5</v>
       </c>
       <c r="F150" t="s">
-        <v>418</v>
+        <v>428</v>
       </c>
       <c r="G150" t="s">
         <v>320</v>
@@ -6893,7 +6881,7 @@
         <v>6</v>
       </c>
       <c r="J150" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
     </row>
     <row r="151" spans="1:10">
@@ -6907,13 +6895,13 @@
         <v>320</v>
       </c>
       <c r="D151">
-        <v>51.5477</v>
+        <v>51.4217</v>
       </c>
       <c r="E151">
         <v>5</v>
       </c>
       <c r="F151" t="s">
-        <v>419</v>
+        <v>429</v>
       </c>
       <c r="G151" t="s">
         <v>320</v>
@@ -6925,7 +6913,7 @@
         <v>5</v>
       </c>
       <c r="J151" t="s">
-        <v>419</v>
+        <v>429</v>
       </c>
     </row>
     <row r="152" spans="1:10">
@@ -6939,13 +6927,13 @@
         <v>320</v>
       </c>
       <c r="D152">
-        <v>51.5797</v>
+        <v>51.5272</v>
       </c>
       <c r="E152">
         <v>5</v>
       </c>
       <c r="F152" t="s">
-        <v>420</v>
+        <v>430</v>
       </c>
       <c r="G152" t="s">
         <v>320</v>
@@ -6957,7 +6945,7 @@
         <v>5</v>
       </c>
       <c r="J152" t="s">
-        <v>420</v>
+        <v>430</v>
       </c>
     </row>
     <row r="153" spans="1:10">
@@ -6971,13 +6959,13 @@
         <v>320</v>
       </c>
       <c r="D153">
-        <v>88.5228</v>
+        <v>88.4464</v>
       </c>
       <c r="E153">
         <v>5</v>
       </c>
       <c r="F153" t="s">
-        <v>416</v>
+        <v>428</v>
       </c>
       <c r="G153" t="s">
         <v>320</v>
@@ -6989,7 +6977,7 @@
         <v>6</v>
       </c>
       <c r="J153" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
     </row>
     <row r="154" spans="1:10">
@@ -7003,13 +6991,13 @@
         <v>320</v>
       </c>
       <c r="D154">
-        <v>37.59</v>
+        <v>37.5351</v>
       </c>
       <c r="E154">
         <v>4</v>
       </c>
       <c r="F154" t="s">
-        <v>421</v>
+        <v>431</v>
       </c>
       <c r="G154" t="s">
         <v>320</v>
@@ -7021,7 +7009,7 @@
         <v>4</v>
       </c>
       <c r="J154" t="s">
-        <v>421</v>
+        <v>431</v>
       </c>
     </row>
     <row r="155" spans="1:10">
@@ -7035,13 +7023,13 @@
         <v>320</v>
       </c>
       <c r="D155">
-        <v>37.5812</v>
+        <v>37.5188</v>
       </c>
       <c r="E155">
         <v>4</v>
       </c>
       <c r="F155" t="s">
-        <v>422</v>
+        <v>431</v>
       </c>
       <c r="G155" t="s">
         <v>320</v>
@@ -7053,7 +7041,7 @@
         <v>4</v>
       </c>
       <c r="J155" t="s">
-        <v>421</v>
+        <v>431</v>
       </c>
     </row>
     <row r="156" spans="1:10">
@@ -7067,22 +7055,25 @@
         <v>320</v>
       </c>
       <c r="D156">
-        <v>88.51909999999999</v>
+        <v>88.4401</v>
       </c>
       <c r="E156">
         <v>5</v>
       </c>
       <c r="F156" t="s">
-        <v>418</v>
+        <v>426</v>
       </c>
       <c r="G156" t="s">
-        <v>514</v>
+        <v>320</v>
       </c>
       <c r="H156">
-        <v>0</v>
+        <v>118.9921</v>
       </c>
       <c r="I156">
-        <v>0</v>
+        <v>6</v>
+      </c>
+      <c r="J156" t="s">
+        <v>555</v>
       </c>
     </row>
     <row r="157" spans="1:10">
@@ -7102,7 +7093,7 @@
         <v>17</v>
       </c>
       <c r="F157" t="s">
-        <v>423</v>
+        <v>432</v>
       </c>
       <c r="G157" t="s">
         <v>320</v>
@@ -7114,7 +7105,7 @@
         <v>14</v>
       </c>
       <c r="J157" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
     </row>
     <row r="158" spans="1:10">
@@ -7128,13 +7119,13 @@
         <v>320</v>
       </c>
       <c r="D158">
-        <v>125.7244</v>
+        <v>125.6299</v>
       </c>
       <c r="E158">
         <v>10</v>
       </c>
       <c r="F158" t="s">
-        <v>424</v>
+        <v>433</v>
       </c>
       <c r="G158" t="s">
         <v>320</v>
@@ -7146,7 +7137,7 @@
         <v>10</v>
       </c>
       <c r="J158" t="s">
-        <v>424</v>
+        <v>433</v>
       </c>
     </row>
     <row r="159" spans="1:10">
@@ -7160,13 +7151,13 @@
         <v>320</v>
       </c>
       <c r="D159">
-        <v>122.999</v>
+        <v>122.9357</v>
       </c>
       <c r="E159">
         <v>10</v>
       </c>
       <c r="F159" t="s">
-        <v>425</v>
+        <v>434</v>
       </c>
       <c r="G159" t="s">
         <v>320</v>
@@ -7178,7 +7169,7 @@
         <v>10</v>
       </c>
       <c r="J159" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
     </row>
     <row r="160" spans="1:10">
@@ -7192,13 +7183,13 @@
         <v>320</v>
       </c>
       <c r="D160">
-        <v>123.0118</v>
+        <v>122.9671</v>
       </c>
       <c r="E160">
         <v>10</v>
       </c>
       <c r="F160" t="s">
-        <v>425</v>
+        <v>434</v>
       </c>
       <c r="G160" t="s">
         <v>320</v>
@@ -7210,7 +7201,7 @@
         <v>10</v>
       </c>
       <c r="J160" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
     </row>
     <row r="161" spans="1:10">
@@ -7224,13 +7215,13 @@
         <v>320</v>
       </c>
       <c r="D161">
-        <v>123.0256</v>
+        <v>122.9615</v>
       </c>
       <c r="E161">
         <v>10</v>
       </c>
       <c r="F161" t="s">
-        <v>426</v>
+        <v>435</v>
       </c>
       <c r="G161" t="s">
         <v>320</v>
@@ -7242,7 +7233,7 @@
         <v>10</v>
       </c>
       <c r="J161" t="s">
-        <v>424</v>
+        <v>433</v>
       </c>
     </row>
     <row r="162" spans="1:10">
@@ -7256,13 +7247,13 @@
         <v>320</v>
       </c>
       <c r="D162">
-        <v>4.6106</v>
+        <v>4.5925</v>
       </c>
       <c r="E162">
         <v>13</v>
       </c>
       <c r="F162" t="s">
-        <v>427</v>
+        <v>436</v>
       </c>
       <c r="G162" t="s">
         <v>320</v>
@@ -7274,7 +7265,7 @@
         <v>13</v>
       </c>
       <c r="J162" t="s">
-        <v>557</v>
+        <v>436</v>
       </c>
     </row>
     <row r="163" spans="1:10">
@@ -7288,13 +7279,13 @@
         <v>320</v>
       </c>
       <c r="D163">
-        <v>7.5504</v>
+        <v>7.5088</v>
       </c>
       <c r="E163">
         <v>10</v>
       </c>
       <c r="F163" t="s">
-        <v>428</v>
+        <v>437</v>
       </c>
       <c r="G163" t="s">
         <v>320</v>
@@ -7306,7 +7297,7 @@
         <v>10</v>
       </c>
       <c r="J163" t="s">
-        <v>428</v>
+        <v>437</v>
       </c>
     </row>
     <row r="164" spans="1:10">
@@ -7320,16 +7311,16 @@
         <v>320</v>
       </c>
       <c r="D164">
-        <v>131.0827</v>
+        <v>130.9891</v>
       </c>
       <c r="E164">
         <v>13</v>
       </c>
       <c r="F164" t="s">
-        <v>429</v>
+        <v>438</v>
       </c>
       <c r="G164" t="s">
-        <v>513</v>
+        <v>524</v>
       </c>
       <c r="H164">
         <v>0</v>
@@ -7349,16 +7340,16 @@
         <v>320</v>
       </c>
       <c r="D165">
-        <v>134.098</v>
+        <v>134.056</v>
       </c>
       <c r="E165">
         <v>21</v>
       </c>
       <c r="F165" t="s">
-        <v>430</v>
+        <v>439</v>
       </c>
       <c r="G165" t="s">
-        <v>513</v>
+        <v>524</v>
       </c>
       <c r="H165">
         <v>0</v>
@@ -7384,10 +7375,10 @@
         <v>21</v>
       </c>
       <c r="F166" t="s">
-        <v>430</v>
+        <v>439</v>
       </c>
       <c r="G166" t="s">
-        <v>513</v>
+        <v>524</v>
       </c>
       <c r="H166">
         <v>0</v>
@@ -7407,16 +7398,16 @@
         <v>320</v>
       </c>
       <c r="D167">
-        <v>131.0482</v>
+        <v>131.0071</v>
       </c>
       <c r="E167">
         <v>13</v>
       </c>
       <c r="F167" t="s">
-        <v>431</v>
+        <v>440</v>
       </c>
       <c r="G167" t="s">
-        <v>513</v>
+        <v>524</v>
       </c>
       <c r="H167">
         <v>0</v>
@@ -7436,16 +7427,16 @@
         <v>320</v>
       </c>
       <c r="D168">
-        <v>131.082</v>
+        <v>131.0236</v>
       </c>
       <c r="E168">
         <v>13</v>
       </c>
       <c r="F168" t="s">
-        <v>429</v>
+        <v>438</v>
       </c>
       <c r="G168" t="s">
-        <v>513</v>
+        <v>524</v>
       </c>
       <c r="H168">
         <v>0</v>
@@ -7471,10 +7462,10 @@
         <v>15</v>
       </c>
       <c r="F169" t="s">
-        <v>432</v>
+        <v>441</v>
       </c>
       <c r="G169" t="s">
-        <v>513</v>
+        <v>524</v>
       </c>
       <c r="H169">
         <v>0</v>
@@ -7494,13 +7485,13 @@
         <v>320</v>
       </c>
       <c r="D170">
-        <v>75.9221</v>
+        <v>75.8609</v>
       </c>
       <c r="E170">
         <v>5</v>
       </c>
       <c r="F170" t="s">
-        <v>433</v>
+        <v>442</v>
       </c>
       <c r="G170" t="s">
         <v>320</v>
@@ -7512,7 +7503,7 @@
         <v>5</v>
       </c>
       <c r="J170" t="s">
-        <v>433</v>
+        <v>442</v>
       </c>
     </row>
     <row r="171" spans="1:10">
@@ -7526,16 +7517,16 @@
         <v>320</v>
       </c>
       <c r="D171">
-        <v>131.0492</v>
+        <v>130.9859</v>
       </c>
       <c r="E171">
         <v>13</v>
       </c>
       <c r="F171" t="s">
-        <v>431</v>
+        <v>438</v>
       </c>
       <c r="G171" t="s">
-        <v>513</v>
+        <v>524</v>
       </c>
       <c r="H171">
         <v>0</v>
@@ -7561,10 +7552,10 @@
         <v>15</v>
       </c>
       <c r="F172" t="s">
-        <v>432</v>
+        <v>441</v>
       </c>
       <c r="G172" t="s">
-        <v>513</v>
+        <v>524</v>
       </c>
       <c r="H172">
         <v>0</v>
@@ -7590,10 +7581,10 @@
         <v>15</v>
       </c>
       <c r="F173" t="s">
-        <v>434</v>
+        <v>443</v>
       </c>
       <c r="G173" t="s">
-        <v>513</v>
+        <v>524</v>
       </c>
       <c r="H173">
         <v>0</v>
@@ -7613,13 +7604,13 @@
         <v>320</v>
       </c>
       <c r="D174">
-        <v>41.9061</v>
+        <v>41.8618</v>
       </c>
       <c r="E174">
         <v>7</v>
       </c>
       <c r="F174" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="G174" t="s">
         <v>320</v>
@@ -7631,7 +7622,7 @@
         <v>7</v>
       </c>
       <c r="J174" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="175" spans="1:10">
@@ -7651,7 +7642,7 @@
         <v>11</v>
       </c>
       <c r="F175" t="s">
-        <v>435</v>
+        <v>444</v>
       </c>
       <c r="G175" t="s">
         <v>320</v>
@@ -7663,7 +7654,7 @@
         <v>11</v>
       </c>
       <c r="J175" t="s">
-        <v>435</v>
+        <v>444</v>
       </c>
     </row>
     <row r="176" spans="1:10">
@@ -7677,16 +7668,16 @@
         <v>320</v>
       </c>
       <c r="D176">
-        <v>131.0726</v>
+        <v>131.0294</v>
       </c>
       <c r="E176">
         <v>13</v>
       </c>
       <c r="F176" t="s">
-        <v>431</v>
+        <v>440</v>
       </c>
       <c r="G176" t="s">
-        <v>513</v>
+        <v>524</v>
       </c>
       <c r="H176">
         <v>0</v>
@@ -7706,13 +7697,13 @@
         <v>320</v>
       </c>
       <c r="D177">
-        <v>75.861</v>
+        <v>75.82940000000001</v>
       </c>
       <c r="E177">
         <v>5</v>
       </c>
       <c r="F177" t="s">
-        <v>436</v>
+        <v>445</v>
       </c>
       <c r="G177" t="s">
         <v>320</v>
@@ -7724,7 +7715,7 @@
         <v>5</v>
       </c>
       <c r="J177" t="s">
-        <v>436</v>
+        <v>445</v>
       </c>
     </row>
     <row r="178" spans="1:10">
@@ -7738,13 +7729,13 @@
         <v>320</v>
       </c>
       <c r="D178">
-        <v>75.8994</v>
+        <v>75.83750000000001</v>
       </c>
       <c r="E178">
         <v>5</v>
       </c>
       <c r="F178" t="s">
-        <v>436</v>
+        <v>445</v>
       </c>
       <c r="G178" t="s">
         <v>320</v>
@@ -7756,7 +7747,7 @@
         <v>5</v>
       </c>
       <c r="J178" t="s">
-        <v>436</v>
+        <v>445</v>
       </c>
     </row>
     <row r="179" spans="1:10">
@@ -7770,16 +7761,16 @@
         <v>320</v>
       </c>
       <c r="D179">
-        <v>131.071</v>
+        <v>131.0117</v>
       </c>
       <c r="E179">
         <v>13</v>
       </c>
       <c r="F179" t="s">
-        <v>431</v>
+        <v>440</v>
       </c>
       <c r="G179" t="s">
-        <v>513</v>
+        <v>524</v>
       </c>
       <c r="H179">
         <v>0</v>
@@ -7799,13 +7790,13 @@
         <v>320</v>
       </c>
       <c r="D180">
-        <v>3.696</v>
+        <v>6.267</v>
       </c>
       <c r="E180">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="F180" t="s">
-        <v>437</v>
+        <v>446</v>
       </c>
       <c r="G180" t="s">
         <v>320</v>
@@ -7817,7 +7808,7 @@
         <v>16</v>
       </c>
       <c r="J180" t="s">
-        <v>558</v>
+        <v>446</v>
       </c>
     </row>
     <row r="181" spans="1:10">
@@ -7837,10 +7828,10 @@
         <v>13</v>
       </c>
       <c r="F181" t="s">
-        <v>431</v>
+        <v>440</v>
       </c>
       <c r="G181" t="s">
-        <v>513</v>
+        <v>524</v>
       </c>
       <c r="H181">
         <v>0</v>
@@ -7860,13 +7851,13 @@
         <v>320</v>
       </c>
       <c r="D182">
-        <v>4.0103</v>
+        <v>3.9679</v>
       </c>
       <c r="E182">
         <v>6</v>
       </c>
       <c r="F182" t="s">
-        <v>438</v>
+        <v>447</v>
       </c>
       <c r="G182" t="s">
         <v>320</v>
@@ -7878,7 +7869,7 @@
         <v>6</v>
       </c>
       <c r="J182" t="s">
-        <v>438</v>
+        <v>447</v>
       </c>
     </row>
     <row r="183" spans="1:10">
@@ -7892,16 +7883,16 @@
         <v>320</v>
       </c>
       <c r="D183">
-        <v>131.0219</v>
+        <v>131.0013</v>
       </c>
       <c r="E183">
         <v>13</v>
       </c>
       <c r="F183" t="s">
-        <v>429</v>
+        <v>440</v>
       </c>
       <c r="G183" t="s">
-        <v>513</v>
+        <v>524</v>
       </c>
       <c r="H183">
         <v>0</v>
@@ -7921,13 +7912,13 @@
         <v>320</v>
       </c>
       <c r="D184">
-        <v>61.5271</v>
+        <v>61.4663</v>
       </c>
       <c r="E184">
         <v>9</v>
       </c>
       <c r="F184" t="s">
-        <v>439</v>
+        <v>351</v>
       </c>
       <c r="G184" t="s">
         <v>320</v>
@@ -7939,7 +7930,7 @@
         <v>18</v>
       </c>
       <c r="J184" t="s">
-        <v>520</v>
+        <v>529</v>
       </c>
     </row>
     <row r="185" spans="1:10">
@@ -7953,22 +7944,25 @@
         <v>320</v>
       </c>
       <c r="D185">
-        <v>61.5314</v>
+        <v>61.4353</v>
       </c>
       <c r="E185">
         <v>9</v>
       </c>
       <c r="F185" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="G185" t="s">
-        <v>514</v>
+        <v>320</v>
       </c>
       <c r="H185">
-        <v>0</v>
+        <v>121.579</v>
       </c>
       <c r="I185">
-        <v>0</v>
+        <v>18</v>
+      </c>
+      <c r="J185" t="s">
+        <v>529</v>
       </c>
     </row>
     <row r="186" spans="1:10">
@@ -7982,22 +7976,25 @@
         <v>320</v>
       </c>
       <c r="D186">
-        <v>75.8613</v>
+        <v>75.7633</v>
       </c>
       <c r="E186">
         <v>5</v>
       </c>
       <c r="F186" t="s">
-        <v>436</v>
+        <v>442</v>
       </c>
       <c r="G186" t="s">
-        <v>514</v>
+        <v>320</v>
       </c>
       <c r="H186">
-        <v>0</v>
+        <v>75.7633</v>
       </c>
       <c r="I186">
-        <v>0</v>
+        <v>5</v>
+      </c>
+      <c r="J186" t="s">
+        <v>442</v>
       </c>
     </row>
     <row r="187" spans="1:10">
@@ -8017,7 +8014,7 @@
         <v>7</v>
       </c>
       <c r="F187" t="s">
-        <v>440</v>
+        <v>448</v>
       </c>
       <c r="G187" t="s">
         <v>320</v>
@@ -8029,7 +8026,7 @@
         <v>7</v>
       </c>
       <c r="J187" t="s">
-        <v>440</v>
+        <v>448</v>
       </c>
     </row>
     <row r="188" spans="1:10">
@@ -8043,13 +8040,13 @@
         <v>320</v>
       </c>
       <c r="D188">
-        <v>3.9998</v>
+        <v>3.9596</v>
       </c>
       <c r="E188">
         <v>6</v>
       </c>
       <c r="F188" t="s">
-        <v>441</v>
+        <v>449</v>
       </c>
       <c r="G188" t="s">
         <v>320</v>
@@ -8061,7 +8058,7 @@
         <v>6</v>
       </c>
       <c r="J188" t="s">
-        <v>441</v>
+        <v>449</v>
       </c>
     </row>
     <row r="189" spans="1:10">
@@ -8081,7 +8078,7 @@
         <v>7</v>
       </c>
       <c r="F189" t="s">
-        <v>440</v>
+        <v>448</v>
       </c>
       <c r="G189" t="s">
         <v>320</v>
@@ -8093,7 +8090,7 @@
         <v>7</v>
       </c>
       <c r="J189" t="s">
-        <v>440</v>
+        <v>448</v>
       </c>
     </row>
     <row r="190" spans="1:10">
@@ -8113,7 +8110,7 @@
         <v>11</v>
       </c>
       <c r="F190" t="s">
-        <v>442</v>
+        <v>450</v>
       </c>
       <c r="G190" t="s">
         <v>320</v>
@@ -8125,7 +8122,7 @@
         <v>11</v>
       </c>
       <c r="J190" t="s">
-        <v>442</v>
+        <v>450</v>
       </c>
     </row>
     <row r="191" spans="1:10">
@@ -8139,13 +8136,13 @@
         <v>320</v>
       </c>
       <c r="D191">
-        <v>8.970599999999999</v>
+        <v>8.9254</v>
       </c>
       <c r="E191">
         <v>10</v>
       </c>
       <c r="F191" t="s">
-        <v>443</v>
+        <v>451</v>
       </c>
       <c r="G191" t="s">
         <v>320</v>
@@ -8171,22 +8168,25 @@
         <v>320</v>
       </c>
       <c r="D192">
-        <v>24.2741</v>
+        <v>24.1843</v>
       </c>
       <c r="E192">
         <v>8</v>
       </c>
       <c r="F192" t="s">
-        <v>444</v>
+        <v>337</v>
       </c>
       <c r="G192" t="s">
-        <v>514</v>
+        <v>320</v>
       </c>
       <c r="H192">
-        <v>0</v>
+        <v>110.4327</v>
       </c>
       <c r="I192">
-        <v>0</v>
+        <v>15</v>
+      </c>
+      <c r="J192" t="s">
+        <v>528</v>
       </c>
     </row>
     <row r="193" spans="1:10">
@@ -8200,7 +8200,7 @@
         <v>320</v>
       </c>
       <c r="D193">
-        <v>108.884</v>
+        <v>108.818</v>
       </c>
       <c r="E193">
         <v>9</v>
@@ -8209,13 +8209,16 @@
         <v>335</v>
       </c>
       <c r="G193" t="s">
-        <v>514</v>
+        <v>320</v>
       </c>
       <c r="H193">
-        <v>0</v>
+        <v>108.818</v>
       </c>
       <c r="I193">
-        <v>0</v>
+        <v>9</v>
+      </c>
+      <c r="J193" t="s">
+        <v>335</v>
       </c>
     </row>
     <row r="194" spans="1:10">
@@ -8229,22 +8232,25 @@
         <v>320</v>
       </c>
       <c r="D194">
-        <v>143.2475</v>
+        <v>143.1893</v>
       </c>
       <c r="E194">
         <v>11</v>
       </c>
       <c r="F194" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="G194" t="s">
-        <v>514</v>
+        <v>320</v>
       </c>
       <c r="H194">
-        <v>0</v>
+        <v>143.1893</v>
       </c>
       <c r="I194">
-        <v>0</v>
+        <v>11</v>
+      </c>
+      <c r="J194" t="s">
+        <v>334</v>
       </c>
     </row>
     <row r="195" spans="1:10">
@@ -8258,22 +8264,25 @@
         <v>320</v>
       </c>
       <c r="D195">
-        <v>143.2498</v>
+        <v>143.1918</v>
       </c>
       <c r="E195">
         <v>11</v>
       </c>
       <c r="F195" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="G195" t="s">
-        <v>514</v>
+        <v>320</v>
       </c>
       <c r="H195">
-        <v>0</v>
+        <v>143.1918</v>
       </c>
       <c r="I195">
-        <v>0</v>
+        <v>11</v>
+      </c>
+      <c r="J195" t="s">
+        <v>334</v>
       </c>
     </row>
     <row r="196" spans="1:10">
@@ -8287,22 +8296,25 @@
         <v>320</v>
       </c>
       <c r="D196">
-        <v>86.9909</v>
+        <v>86.8985</v>
       </c>
       <c r="E196">
         <v>9</v>
       </c>
       <c r="F196" t="s">
-        <v>336</v>
+        <v>347</v>
       </c>
       <c r="G196" t="s">
-        <v>514</v>
+        <v>320</v>
       </c>
       <c r="H196">
-        <v>0</v>
+        <v>110.4293</v>
       </c>
       <c r="I196">
-        <v>0</v>
+        <v>15</v>
+      </c>
+      <c r="J196" t="s">
+        <v>528</v>
       </c>
     </row>
     <row r="197" spans="1:10">
@@ -8316,7 +8328,7 @@
         <v>320</v>
       </c>
       <c r="D197">
-        <v>87.0244</v>
+        <v>86.9648</v>
       </c>
       <c r="E197">
         <v>9</v>
@@ -8325,13 +8337,16 @@
         <v>336</v>
       </c>
       <c r="G197" t="s">
-        <v>514</v>
+        <v>320</v>
       </c>
       <c r="H197">
-        <v>0</v>
+        <v>110.4956</v>
       </c>
       <c r="I197">
-        <v>0</v>
+        <v>15</v>
+      </c>
+      <c r="J197" t="s">
+        <v>527</v>
       </c>
     </row>
     <row r="198" spans="1:10">
@@ -8345,7 +8360,7 @@
         <v>320</v>
       </c>
       <c r="D198">
-        <v>87.0052</v>
+        <v>86.9297</v>
       </c>
       <c r="E198">
         <v>9</v>
@@ -8363,7 +8378,7 @@
         <v>15</v>
       </c>
       <c r="J198" t="s">
-        <v>517</v>
+        <v>527</v>
       </c>
     </row>
     <row r="199" spans="1:10">
@@ -8377,7 +8392,7 @@
         <v>320</v>
       </c>
       <c r="D199">
-        <v>87.0057</v>
+        <v>86.9315</v>
       </c>
       <c r="E199">
         <v>9</v>
@@ -8395,7 +8410,7 @@
         <v>15</v>
       </c>
       <c r="J199" t="s">
-        <v>517</v>
+        <v>527</v>
       </c>
     </row>
     <row r="200" spans="1:10">
@@ -8409,22 +8424,25 @@
         <v>320</v>
       </c>
       <c r="D200">
-        <v>86.9914</v>
+        <v>86.9034</v>
       </c>
       <c r="E200">
         <v>9</v>
       </c>
       <c r="F200" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="G200" t="s">
-        <v>514</v>
+        <v>320</v>
       </c>
       <c r="H200">
-        <v>0</v>
+        <v>110.4342</v>
       </c>
       <c r="I200">
-        <v>0</v>
+        <v>15</v>
+      </c>
+      <c r="J200" t="s">
+        <v>528</v>
       </c>
     </row>
     <row r="201" spans="1:10">
@@ -8438,7 +8456,7 @@
         <v>320</v>
       </c>
       <c r="D201">
-        <v>86.9931</v>
+        <v>86.9027</v>
       </c>
       <c r="E201">
         <v>9</v>
@@ -8447,13 +8465,16 @@
         <v>336</v>
       </c>
       <c r="G201" t="s">
-        <v>514</v>
+        <v>320</v>
       </c>
       <c r="H201">
-        <v>0</v>
+        <v>110.4334</v>
       </c>
       <c r="I201">
-        <v>0</v>
+        <v>15</v>
+      </c>
+      <c r="J201" t="s">
+        <v>527</v>
       </c>
     </row>
     <row r="202" spans="1:10">
@@ -8467,7 +8488,7 @@
         <v>320</v>
       </c>
       <c r="D202">
-        <v>86.989</v>
+        <v>86.8976</v>
       </c>
       <c r="E202">
         <v>9</v>
@@ -8476,13 +8497,16 @@
         <v>336</v>
       </c>
       <c r="G202" t="s">
-        <v>514</v>
+        <v>320</v>
       </c>
       <c r="H202">
-        <v>0</v>
+        <v>110.4284</v>
       </c>
       <c r="I202">
-        <v>0</v>
+        <v>15</v>
+      </c>
+      <c r="J202" t="s">
+        <v>527</v>
       </c>
     </row>
     <row r="203" spans="1:10">
@@ -8496,13 +8520,13 @@
         <v>320</v>
       </c>
       <c r="D203">
-        <v>7.2866</v>
+        <v>7.1622</v>
       </c>
       <c r="E203">
         <v>6</v>
       </c>
       <c r="F203" t="s">
-        <v>445</v>
+        <v>452</v>
       </c>
       <c r="G203" t="s">
         <v>320</v>
@@ -8514,7 +8538,7 @@
         <v>6</v>
       </c>
       <c r="J203" t="s">
-        <v>445</v>
+        <v>452</v>
       </c>
     </row>
     <row r="204" spans="1:10">
@@ -8528,13 +8552,13 @@
         <v>320</v>
       </c>
       <c r="D204">
-        <v>67.93770000000001</v>
+        <v>67.892</v>
       </c>
       <c r="E204">
         <v>9</v>
       </c>
       <c r="F204" t="s">
-        <v>446</v>
+        <v>453</v>
       </c>
       <c r="G204" t="s">
         <v>320</v>
@@ -8546,7 +8570,7 @@
         <v>9</v>
       </c>
       <c r="J204" t="s">
-        <v>446</v>
+        <v>453</v>
       </c>
     </row>
     <row r="205" spans="1:10">
@@ -8560,7 +8584,7 @@
         <v>320</v>
       </c>
       <c r="D205">
-        <v>87.02290000000001</v>
+        <v>86.96550000000001</v>
       </c>
       <c r="E205">
         <v>9</v>
@@ -8569,13 +8593,16 @@
         <v>336</v>
       </c>
       <c r="G205" t="s">
-        <v>514</v>
+        <v>320</v>
       </c>
       <c r="H205">
-        <v>0</v>
+        <v>110.4963</v>
       </c>
       <c r="I205">
-        <v>0</v>
+        <v>15</v>
+      </c>
+      <c r="J205" t="s">
+        <v>527</v>
       </c>
     </row>
     <row r="206" spans="1:10">
@@ -8589,22 +8616,25 @@
         <v>320</v>
       </c>
       <c r="D206">
-        <v>24.2771</v>
+        <v>24.1904</v>
       </c>
       <c r="E206">
         <v>8</v>
       </c>
       <c r="F206" t="s">
-        <v>444</v>
+        <v>454</v>
       </c>
       <c r="G206" t="s">
-        <v>514</v>
+        <v>320</v>
       </c>
       <c r="H206">
-        <v>0</v>
+        <v>110.4387</v>
       </c>
       <c r="I206">
-        <v>0</v>
+        <v>15</v>
+      </c>
+      <c r="J206" t="s">
+        <v>560</v>
       </c>
     </row>
     <row r="207" spans="1:10">
@@ -8618,13 +8648,13 @@
         <v>320</v>
       </c>
       <c r="D207">
-        <v>54.0733</v>
+        <v>53.9979</v>
       </c>
       <c r="E207">
         <v>15</v>
       </c>
       <c r="F207" t="s">
-        <v>447</v>
+        <v>455</v>
       </c>
       <c r="G207" t="s">
         <v>320</v>
@@ -8650,13 +8680,13 @@
         <v>320</v>
       </c>
       <c r="D208">
-        <v>8.166499999999999</v>
+        <v>8.1121</v>
       </c>
       <c r="E208">
         <v>5</v>
       </c>
       <c r="F208" t="s">
-        <v>448</v>
+        <v>456</v>
       </c>
       <c r="G208" t="s">
         <v>320</v>
@@ -8668,7 +8698,7 @@
         <v>5</v>
       </c>
       <c r="J208" t="s">
-        <v>448</v>
+        <v>456</v>
       </c>
     </row>
     <row r="209" spans="1:10">
@@ -8682,22 +8712,25 @@
         <v>320</v>
       </c>
       <c r="D209">
-        <v>64.3768</v>
+        <v>64.3361</v>
       </c>
       <c r="E209">
         <v>7</v>
       </c>
       <c r="F209" t="s">
-        <v>449</v>
+        <v>457</v>
       </c>
       <c r="G209" t="s">
-        <v>514</v>
+        <v>320</v>
       </c>
       <c r="H209">
-        <v>0</v>
+        <v>64.3361</v>
       </c>
       <c r="I209">
-        <v>0</v>
+        <v>7</v>
+      </c>
+      <c r="J209" t="s">
+        <v>457</v>
       </c>
     </row>
     <row r="210" spans="1:10">
@@ -8717,7 +8750,7 @@
         <v>11</v>
       </c>
       <c r="F210" t="s">
-        <v>450</v>
+        <v>458</v>
       </c>
       <c r="G210" t="s">
         <v>320</v>
@@ -8743,13 +8776,13 @@
         <v>320</v>
       </c>
       <c r="D211">
-        <v>107.5523</v>
+        <v>107.4951</v>
       </c>
       <c r="E211">
         <v>7</v>
       </c>
       <c r="F211" t="s">
-        <v>451</v>
+        <v>459</v>
       </c>
       <c r="G211" t="s">
         <v>320</v>
@@ -8761,7 +8794,7 @@
         <v>7</v>
       </c>
       <c r="J211" t="s">
-        <v>451</v>
+        <v>459</v>
       </c>
     </row>
     <row r="212" spans="1:10">
@@ -8781,10 +8814,10 @@
         <v>17</v>
       </c>
       <c r="F212" t="s">
-        <v>452</v>
+        <v>460</v>
       </c>
       <c r="G212" t="s">
-        <v>513</v>
+        <v>524</v>
       </c>
       <c r="H212">
         <v>0</v>
@@ -8810,10 +8843,10 @@
         <v>17</v>
       </c>
       <c r="F213" t="s">
-        <v>452</v>
+        <v>460</v>
       </c>
       <c r="G213" t="s">
-        <v>513</v>
+        <v>524</v>
       </c>
       <c r="H213">
         <v>0</v>
@@ -8839,7 +8872,7 @@
         <v>9</v>
       </c>
       <c r="F214" t="s">
-        <v>453</v>
+        <v>461</v>
       </c>
       <c r="G214" t="s">
         <v>320</v>
@@ -8851,7 +8884,7 @@
         <v>9</v>
       </c>
       <c r="J214" t="s">
-        <v>453</v>
+        <v>461</v>
       </c>
     </row>
     <row r="215" spans="1:10">
@@ -8865,22 +8898,25 @@
         <v>320</v>
       </c>
       <c r="D215">
-        <v>54.058</v>
+        <v>53.9665</v>
       </c>
       <c r="E215">
         <v>15</v>
       </c>
       <c r="F215" t="s">
-        <v>454</v>
+        <v>462</v>
       </c>
       <c r="G215" t="s">
-        <v>514</v>
+        <v>320</v>
       </c>
       <c r="H215">
-        <v>0</v>
+        <v>110.4414</v>
       </c>
       <c r="I215">
-        <v>0</v>
+        <v>15</v>
+      </c>
+      <c r="J215" t="s">
+        <v>528</v>
       </c>
     </row>
     <row r="216" spans="1:10">
@@ -8894,22 +8930,25 @@
         <v>320</v>
       </c>
       <c r="D216">
-        <v>24.2754</v>
+        <v>24.185</v>
       </c>
       <c r="E216">
         <v>8</v>
       </c>
       <c r="F216" t="s">
-        <v>444</v>
+        <v>454</v>
       </c>
       <c r="G216" t="s">
-        <v>514</v>
+        <v>320</v>
       </c>
       <c r="H216">
-        <v>0</v>
+        <v>110.4334</v>
       </c>
       <c r="I216">
-        <v>0</v>
+        <v>15</v>
+      </c>
+      <c r="J216" t="s">
+        <v>560</v>
       </c>
     </row>
     <row r="217" spans="1:10">
@@ -8929,7 +8968,7 @@
         <v>9</v>
       </c>
       <c r="F217" t="s">
-        <v>446</v>
+        <v>453</v>
       </c>
       <c r="G217" t="s">
         <v>320</v>
@@ -8941,7 +8980,7 @@
         <v>9</v>
       </c>
       <c r="J217" t="s">
-        <v>446</v>
+        <v>453</v>
       </c>
     </row>
     <row r="218" spans="1:10">
@@ -8961,7 +9000,7 @@
         <v>8</v>
       </c>
       <c r="F218" t="s">
-        <v>455</v>
+        <v>463</v>
       </c>
       <c r="G218" t="s">
         <v>320</v>
@@ -8973,7 +9012,7 @@
         <v>8</v>
       </c>
       <c r="J218" t="s">
-        <v>455</v>
+        <v>463</v>
       </c>
     </row>
     <row r="219" spans="1:10">
@@ -8993,7 +9032,7 @@
         <v>14</v>
       </c>
       <c r="F219" t="s">
-        <v>456</v>
+        <v>464</v>
       </c>
       <c r="G219" t="s">
         <v>320</v>
@@ -9005,7 +9044,7 @@
         <v>14</v>
       </c>
       <c r="J219" t="s">
-        <v>456</v>
+        <v>464</v>
       </c>
     </row>
     <row r="220" spans="1:10">
@@ -9019,13 +9058,13 @@
         <v>320</v>
       </c>
       <c r="D220">
-        <v>73.3948</v>
+        <v>73.3646</v>
       </c>
       <c r="E220">
         <v>10</v>
       </c>
       <c r="F220" t="s">
-        <v>457</v>
+        <v>465</v>
       </c>
       <c r="G220" t="s">
         <v>320</v>
@@ -9037,7 +9076,7 @@
         <v>10</v>
       </c>
       <c r="J220" t="s">
-        <v>457</v>
+        <v>465</v>
       </c>
     </row>
     <row r="221" spans="1:10">
@@ -9051,22 +9090,25 @@
         <v>320</v>
       </c>
       <c r="D221">
-        <v>54.0832</v>
+        <v>54.025</v>
       </c>
       <c r="E221">
         <v>15</v>
       </c>
       <c r="F221" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="G221" t="s">
-        <v>514</v>
+        <v>320</v>
       </c>
       <c r="H221">
-        <v>0</v>
+        <v>110.5</v>
       </c>
       <c r="I221">
-        <v>0</v>
+        <v>15</v>
+      </c>
+      <c r="J221" t="s">
+        <v>560</v>
       </c>
     </row>
     <row r="222" spans="1:10">
@@ -9080,13 +9122,13 @@
         <v>320</v>
       </c>
       <c r="D222">
-        <v>67.95050000000001</v>
+        <v>67.8056</v>
       </c>
       <c r="E222">
         <v>9</v>
       </c>
       <c r="F222" t="s">
-        <v>446</v>
+        <v>466</v>
       </c>
       <c r="G222" t="s">
         <v>320</v>
@@ -9098,7 +9140,7 @@
         <v>9</v>
       </c>
       <c r="J222" t="s">
-        <v>562</v>
+        <v>466</v>
       </c>
     </row>
     <row r="223" spans="1:10">
@@ -9112,13 +9154,13 @@
         <v>320</v>
       </c>
       <c r="D223">
-        <v>54.0624</v>
+        <v>53.9869</v>
       </c>
       <c r="E223">
         <v>15</v>
       </c>
       <c r="F223" t="s">
-        <v>447</v>
+        <v>455</v>
       </c>
       <c r="G223" t="s">
         <v>320</v>
@@ -9150,7 +9192,7 @@
         <v>14</v>
       </c>
       <c r="F224" t="s">
-        <v>458</v>
+        <v>467</v>
       </c>
       <c r="G224" t="s">
         <v>320</v>
@@ -9162,7 +9204,7 @@
         <v>16</v>
       </c>
       <c r="J224" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="225" spans="1:10">
@@ -9182,10 +9224,10 @@
         <v>17</v>
       </c>
       <c r="F225" t="s">
-        <v>452</v>
+        <v>460</v>
       </c>
       <c r="G225" t="s">
-        <v>513</v>
+        <v>524</v>
       </c>
       <c r="H225">
         <v>0</v>
@@ -9211,7 +9253,7 @@
         <v>9</v>
       </c>
       <c r="F226" t="s">
-        <v>459</v>
+        <v>468</v>
       </c>
       <c r="G226" t="s">
         <v>320</v>
@@ -9223,7 +9265,7 @@
         <v>9</v>
       </c>
       <c r="J226" t="s">
-        <v>459</v>
+        <v>468</v>
       </c>
     </row>
     <row r="227" spans="1:10">
@@ -9237,22 +9279,25 @@
         <v>320</v>
       </c>
       <c r="D227">
-        <v>64.3909</v>
+        <v>64.29349999999999</v>
       </c>
       <c r="E227">
         <v>7</v>
       </c>
       <c r="F227" t="s">
-        <v>449</v>
+        <v>457</v>
       </c>
       <c r="G227" t="s">
-        <v>514</v>
+        <v>320</v>
       </c>
       <c r="H227">
-        <v>0</v>
+        <v>64.29349999999999</v>
       </c>
       <c r="I227">
-        <v>0</v>
+        <v>7</v>
+      </c>
+      <c r="J227" t="s">
+        <v>457</v>
       </c>
     </row>
     <row r="228" spans="1:10">
@@ -9266,13 +9311,13 @@
         <v>320</v>
       </c>
       <c r="D228">
-        <v>95.336</v>
+        <v>95.258</v>
       </c>
       <c r="E228">
         <v>7</v>
       </c>
       <c r="F228" t="s">
-        <v>460</v>
+        <v>469</v>
       </c>
       <c r="G228" t="s">
         <v>320</v>
@@ -9284,7 +9329,7 @@
         <v>7</v>
       </c>
       <c r="J228" t="s">
-        <v>460</v>
+        <v>469</v>
       </c>
     </row>
     <row r="229" spans="1:10">
@@ -9298,13 +9343,13 @@
         <v>320</v>
       </c>
       <c r="D229">
-        <v>67.93729999999999</v>
+        <v>67.8916</v>
       </c>
       <c r="E229">
         <v>9</v>
       </c>
       <c r="F229" t="s">
-        <v>446</v>
+        <v>453</v>
       </c>
       <c r="G229" t="s">
         <v>320</v>
@@ -9316,7 +9361,7 @@
         <v>9</v>
       </c>
       <c r="J229" t="s">
-        <v>446</v>
+        <v>453</v>
       </c>
     </row>
     <row r="230" spans="1:10">
@@ -9330,13 +9375,13 @@
         <v>320</v>
       </c>
       <c r="D230">
-        <v>95.349</v>
+        <v>95.2825</v>
       </c>
       <c r="E230">
         <v>7</v>
       </c>
       <c r="F230" t="s">
-        <v>460</v>
+        <v>469</v>
       </c>
       <c r="G230" t="s">
         <v>320</v>
@@ -9348,7 +9393,7 @@
         <v>7</v>
       </c>
       <c r="J230" t="s">
-        <v>460</v>
+        <v>469</v>
       </c>
     </row>
     <row r="231" spans="1:10">
@@ -9368,7 +9413,7 @@
         <v>1</v>
       </c>
       <c r="F231" t="s">
-        <v>461</v>
+        <v>470</v>
       </c>
       <c r="G231" t="s">
         <v>320</v>
@@ -9380,7 +9425,7 @@
         <v>1</v>
       </c>
       <c r="J231" t="s">
-        <v>461</v>
+        <v>470</v>
       </c>
     </row>
     <row r="232" spans="1:10">
@@ -9400,7 +9445,7 @@
         <v>22</v>
       </c>
       <c r="F232" t="s">
-        <v>462</v>
+        <v>471</v>
       </c>
       <c r="G232" t="s">
         <v>320</v>
@@ -9412,7 +9457,7 @@
         <v>26</v>
       </c>
       <c r="J232" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
     </row>
     <row r="233" spans="1:10">
@@ -9432,7 +9477,7 @@
         <v>22</v>
       </c>
       <c r="F233" t="s">
-        <v>463</v>
+        <v>472</v>
       </c>
       <c r="G233" t="s">
         <v>320</v>
@@ -9444,7 +9489,7 @@
         <v>26</v>
       </c>
       <c r="J233" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
     </row>
     <row r="234" spans="1:10">
@@ -9458,13 +9503,13 @@
         <v>320</v>
       </c>
       <c r="D234">
-        <v>7.285</v>
+        <v>7.1636</v>
       </c>
       <c r="E234">
         <v>6</v>
       </c>
       <c r="F234" t="s">
-        <v>445</v>
+        <v>452</v>
       </c>
       <c r="G234" t="s">
         <v>320</v>
@@ -9476,7 +9521,7 @@
         <v>6</v>
       </c>
       <c r="J234" t="s">
-        <v>445</v>
+        <v>452</v>
       </c>
     </row>
     <row r="235" spans="1:10">
@@ -9496,7 +9541,7 @@
         <v>22</v>
       </c>
       <c r="F235" t="s">
-        <v>464</v>
+        <v>473</v>
       </c>
       <c r="G235" t="s">
         <v>320</v>
@@ -9508,7 +9553,7 @@
         <v>26</v>
       </c>
       <c r="J235" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
     </row>
     <row r="236" spans="1:10">
@@ -9528,7 +9573,7 @@
         <v>22</v>
       </c>
       <c r="F236" t="s">
-        <v>465</v>
+        <v>474</v>
       </c>
       <c r="G236" t="s">
         <v>320</v>
@@ -9540,7 +9585,7 @@
         <v>26</v>
       </c>
       <c r="J236" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="237" spans="1:10">
@@ -9554,13 +9599,13 @@
         <v>320</v>
       </c>
       <c r="D237">
-        <v>107.563</v>
+        <v>107.5188</v>
       </c>
       <c r="E237">
         <v>7</v>
       </c>
       <c r="F237" t="s">
-        <v>466</v>
+        <v>475</v>
       </c>
       <c r="G237" t="s">
         <v>320</v>
@@ -9572,7 +9617,7 @@
         <v>7</v>
       </c>
       <c r="J237" t="s">
-        <v>466</v>
+        <v>475</v>
       </c>
     </row>
     <row r="238" spans="1:10">
@@ -9586,13 +9631,13 @@
         <v>320</v>
       </c>
       <c r="D238">
-        <v>107.5654</v>
+        <v>107.4992</v>
       </c>
       <c r="E238">
         <v>7</v>
       </c>
       <c r="F238" t="s">
-        <v>466</v>
+        <v>475</v>
       </c>
       <c r="G238" t="s">
         <v>320</v>
@@ -9604,7 +9649,7 @@
         <v>7</v>
       </c>
       <c r="J238" t="s">
-        <v>466</v>
+        <v>475</v>
       </c>
     </row>
     <row r="239" spans="1:10">
@@ -9624,7 +9669,7 @@
         <v>6</v>
       </c>
       <c r="F239" t="s">
-        <v>467</v>
+        <v>476</v>
       </c>
       <c r="G239" t="s">
         <v>320</v>
@@ -9636,7 +9681,7 @@
         <v>6</v>
       </c>
       <c r="J239" t="s">
-        <v>467</v>
+        <v>476</v>
       </c>
     </row>
     <row r="240" spans="1:10">
@@ -9656,7 +9701,7 @@
         <v>11</v>
       </c>
       <c r="F240" t="s">
-        <v>468</v>
+        <v>477</v>
       </c>
       <c r="G240" t="s">
         <v>320</v>
@@ -9668,7 +9713,7 @@
         <v>11</v>
       </c>
       <c r="J240" t="s">
-        <v>468</v>
+        <v>477</v>
       </c>
     </row>
     <row r="241" spans="1:10">
@@ -9688,7 +9733,7 @@
         <v>4</v>
       </c>
       <c r="F241" t="s">
-        <v>469</v>
+        <v>478</v>
       </c>
       <c r="G241" t="s">
         <v>320</v>
@@ -9700,7 +9745,7 @@
         <v>4</v>
       </c>
       <c r="J241" t="s">
-        <v>469</v>
+        <v>478</v>
       </c>
     </row>
     <row r="242" spans="1:10">
@@ -9714,13 +9759,13 @@
         <v>320</v>
       </c>
       <c r="D242">
-        <v>54.4125</v>
+        <v>54.3682</v>
       </c>
       <c r="E242">
         <v>10</v>
       </c>
       <c r="F242" t="s">
-        <v>470</v>
+        <v>479</v>
       </c>
       <c r="G242" t="s">
         <v>320</v>
@@ -9732,7 +9777,7 @@
         <v>10</v>
       </c>
       <c r="J242" t="s">
-        <v>470</v>
+        <v>479</v>
       </c>
     </row>
     <row r="243" spans="1:10">
@@ -9746,13 +9791,13 @@
         <v>320</v>
       </c>
       <c r="D243">
-        <v>2.997</v>
+        <v>2.9365</v>
       </c>
       <c r="E243">
         <v>4</v>
       </c>
       <c r="F243" t="s">
-        <v>471</v>
+        <v>480</v>
       </c>
       <c r="G243" t="s">
         <v>320</v>
@@ -9764,7 +9809,7 @@
         <v>4</v>
       </c>
       <c r="J243" t="s">
-        <v>471</v>
+        <v>480</v>
       </c>
     </row>
     <row r="244" spans="1:10">
@@ -9778,13 +9823,13 @@
         <v>320</v>
       </c>
       <c r="D244">
-        <v>54.4122</v>
+        <v>54.3681</v>
       </c>
       <c r="E244">
         <v>10</v>
       </c>
       <c r="F244" t="s">
-        <v>470</v>
+        <v>479</v>
       </c>
       <c r="G244" t="s">
         <v>320</v>
@@ -9796,7 +9841,7 @@
         <v>10</v>
       </c>
       <c r="J244" t="s">
-        <v>470</v>
+        <v>479</v>
       </c>
     </row>
     <row r="245" spans="1:10">
@@ -9810,13 +9855,13 @@
         <v>320</v>
       </c>
       <c r="D245">
-        <v>15.6788</v>
+        <v>15.6132</v>
       </c>
       <c r="E245">
         <v>4</v>
       </c>
       <c r="F245" t="s">
-        <v>472</v>
+        <v>481</v>
       </c>
       <c r="G245" t="s">
         <v>320</v>
@@ -9828,7 +9873,7 @@
         <v>13</v>
       </c>
       <c r="J245" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
     </row>
     <row r="246" spans="1:10">
@@ -9842,13 +9887,13 @@
         <v>320</v>
       </c>
       <c r="D246">
-        <v>0.09320000000000001</v>
+        <v>1.7044</v>
       </c>
       <c r="E246">
         <v>1</v>
       </c>
       <c r="F246" t="s">
-        <v>461</v>
+        <v>482</v>
       </c>
       <c r="G246" t="s">
         <v>320</v>
@@ -9860,7 +9905,7 @@
         <v>1</v>
       </c>
       <c r="J246" t="s">
-        <v>569</v>
+        <v>482</v>
       </c>
     </row>
     <row r="247" spans="1:10">
@@ -9880,7 +9925,7 @@
         <v>11</v>
       </c>
       <c r="F247" t="s">
-        <v>473</v>
+        <v>483</v>
       </c>
       <c r="G247" t="s">
         <v>320</v>
@@ -9892,7 +9937,7 @@
         <v>20</v>
       </c>
       <c r="J247" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
     </row>
     <row r="248" spans="1:10">
@@ -9912,7 +9957,7 @@
         <v>11</v>
       </c>
       <c r="F248" t="s">
-        <v>474</v>
+        <v>484</v>
       </c>
       <c r="G248" t="s">
         <v>320</v>
@@ -9924,7 +9969,7 @@
         <v>20</v>
       </c>
       <c r="J248" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
     </row>
     <row r="249" spans="1:10">
@@ -9938,13 +9983,13 @@
         <v>320</v>
       </c>
       <c r="D249">
-        <v>34.9008</v>
+        <v>34.8143</v>
       </c>
       <c r="E249">
         <v>7</v>
       </c>
       <c r="F249" t="s">
-        <v>475</v>
+        <v>485</v>
       </c>
       <c r="G249" t="s">
         <v>320</v>
@@ -9956,7 +10001,7 @@
         <v>7</v>
       </c>
       <c r="J249" t="s">
-        <v>475</v>
+        <v>485</v>
       </c>
     </row>
     <row r="250" spans="1:10">
@@ -9976,7 +10021,7 @@
         <v>22</v>
       </c>
       <c r="F250" t="s">
-        <v>462</v>
+        <v>471</v>
       </c>
       <c r="G250" t="s">
         <v>320</v>
@@ -9988,7 +10033,7 @@
         <v>26</v>
       </c>
       <c r="J250" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
     </row>
     <row r="251" spans="1:10">
@@ -10008,7 +10053,7 @@
         <v>1</v>
       </c>
       <c r="F251" t="s">
-        <v>461</v>
+        <v>470</v>
       </c>
       <c r="G251" t="s">
         <v>320</v>
@@ -10020,7 +10065,7 @@
         <v>1</v>
       </c>
       <c r="J251" t="s">
-        <v>461</v>
+        <v>470</v>
       </c>
     </row>
     <row r="252" spans="1:10">
@@ -10034,13 +10079,13 @@
         <v>320</v>
       </c>
       <c r="D252">
-        <v>9.6168</v>
+        <v>9.591100000000001</v>
       </c>
       <c r="E252">
         <v>11</v>
       </c>
       <c r="F252" t="s">
-        <v>476</v>
+        <v>486</v>
       </c>
       <c r="G252" t="s">
         <v>320</v>
@@ -10052,7 +10097,7 @@
         <v>11</v>
       </c>
       <c r="J252" t="s">
-        <v>476</v>
+        <v>486</v>
       </c>
     </row>
     <row r="253" spans="1:10">
@@ -10072,7 +10117,7 @@
         <v>11</v>
       </c>
       <c r="F253" t="s">
-        <v>476</v>
+        <v>486</v>
       </c>
       <c r="G253" t="s">
         <v>320</v>
@@ -10084,7 +10129,7 @@
         <v>11</v>
       </c>
       <c r="J253" t="s">
-        <v>476</v>
+        <v>486</v>
       </c>
     </row>
     <row r="254" spans="1:10">
@@ -10104,7 +10149,7 @@
         <v>11</v>
       </c>
       <c r="F254" t="s">
-        <v>477</v>
+        <v>487</v>
       </c>
       <c r="G254" t="s">
         <v>320</v>
@@ -10116,7 +10161,7 @@
         <v>11</v>
       </c>
       <c r="J254" t="s">
-        <v>477</v>
+        <v>487</v>
       </c>
     </row>
     <row r="255" spans="1:10">
@@ -10136,7 +10181,7 @@
         <v>9</v>
       </c>
       <c r="F255" t="s">
-        <v>477</v>
+        <v>487</v>
       </c>
       <c r="G255" t="s">
         <v>320</v>
@@ -10148,7 +10193,7 @@
         <v>9</v>
       </c>
       <c r="J255" t="s">
-        <v>477</v>
+        <v>487</v>
       </c>
     </row>
     <row r="256" spans="1:10">
@@ -10162,13 +10207,13 @@
         <v>320</v>
       </c>
       <c r="D256">
-        <v>191.7361</v>
+        <v>191.6581</v>
       </c>
       <c r="E256">
         <v>13</v>
       </c>
       <c r="F256" t="s">
-        <v>478</v>
+        <v>488</v>
       </c>
       <c r="G256" t="s">
         <v>320</v>
@@ -10180,7 +10225,7 @@
         <v>16</v>
       </c>
       <c r="J256" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="257" spans="1:10">
@@ -10200,10 +10245,10 @@
         <v>17</v>
       </c>
       <c r="F257" t="s">
-        <v>452</v>
+        <v>460</v>
       </c>
       <c r="G257" t="s">
-        <v>513</v>
+        <v>524</v>
       </c>
       <c r="H257">
         <v>0</v>
@@ -10229,7 +10274,7 @@
         <v>6</v>
       </c>
       <c r="F258" t="s">
-        <v>479</v>
+        <v>489</v>
       </c>
       <c r="G258" t="s">
         <v>320</v>
@@ -10241,7 +10286,7 @@
         <v>13</v>
       </c>
       <c r="J258" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
     </row>
     <row r="259" spans="1:10">
@@ -10255,13 +10300,13 @@
         <v>320</v>
       </c>
       <c r="D259">
-        <v>178.8299</v>
+        <v>178.7876</v>
       </c>
       <c r="E259">
         <v>14</v>
       </c>
       <c r="F259" t="s">
-        <v>480</v>
+        <v>490</v>
       </c>
       <c r="G259" t="s">
         <v>320</v>
@@ -10273,7 +10318,7 @@
         <v>16</v>
       </c>
       <c r="J259" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
     </row>
     <row r="260" spans="1:10">
@@ -10287,13 +10332,13 @@
         <v>320</v>
       </c>
       <c r="D260">
-        <v>178.8396</v>
+        <v>178.7607</v>
       </c>
       <c r="E260">
         <v>14</v>
       </c>
       <c r="F260" t="s">
-        <v>481</v>
+        <v>491</v>
       </c>
       <c r="G260" t="s">
         <v>320</v>
@@ -10305,7 +10350,7 @@
         <v>16</v>
       </c>
       <c r="J260" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
     </row>
     <row r="261" spans="1:10">
@@ -10319,13 +10364,13 @@
         <v>320</v>
       </c>
       <c r="D261">
-        <v>8.7174</v>
+        <v>8.6546</v>
       </c>
       <c r="E261">
         <v>7</v>
       </c>
       <c r="F261" t="s">
-        <v>482</v>
+        <v>492</v>
       </c>
       <c r="G261" t="s">
         <v>320</v>
@@ -10337,7 +10382,7 @@
         <v>7</v>
       </c>
       <c r="J261" t="s">
-        <v>482</v>
+        <v>492</v>
       </c>
     </row>
     <row r="262" spans="1:10">
@@ -10357,10 +10402,10 @@
         <v>17</v>
       </c>
       <c r="F262" t="s">
-        <v>452</v>
+        <v>460</v>
       </c>
       <c r="G262" t="s">
-        <v>513</v>
+        <v>524</v>
       </c>
       <c r="H262">
         <v>0</v>
@@ -10386,7 +10431,7 @@
         <v>22</v>
       </c>
       <c r="F263" t="s">
-        <v>462</v>
+        <v>471</v>
       </c>
       <c r="G263" t="s">
         <v>320</v>
@@ -10398,7 +10443,7 @@
         <v>26</v>
       </c>
       <c r="J263" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
     </row>
     <row r="264" spans="1:10">
@@ -10418,7 +10463,7 @@
         <v>8</v>
       </c>
       <c r="F264" t="s">
-        <v>483</v>
+        <v>493</v>
       </c>
       <c r="G264" t="s">
         <v>320</v>
@@ -10430,7 +10475,7 @@
         <v>8</v>
       </c>
       <c r="J264" t="s">
-        <v>483</v>
+        <v>493</v>
       </c>
     </row>
     <row r="265" spans="1:10">
@@ -10450,7 +10495,7 @@
         <v>8</v>
       </c>
       <c r="F265" t="s">
-        <v>483</v>
+        <v>493</v>
       </c>
       <c r="G265" t="s">
         <v>320</v>
@@ -10462,7 +10507,7 @@
         <v>8</v>
       </c>
       <c r="J265" t="s">
-        <v>483</v>
+        <v>493</v>
       </c>
     </row>
     <row r="266" spans="1:10">
@@ -10482,7 +10527,7 @@
         <v>10</v>
       </c>
       <c r="F266" t="s">
-        <v>484</v>
+        <v>494</v>
       </c>
       <c r="G266" t="s">
         <v>320</v>
@@ -10494,7 +10539,7 @@
         <v>10</v>
       </c>
       <c r="J266" t="s">
-        <v>484</v>
+        <v>494</v>
       </c>
     </row>
     <row r="267" spans="1:10">
@@ -10508,16 +10553,16 @@
         <v>320</v>
       </c>
       <c r="D267">
-        <v>124.7989</v>
+        <v>124.6978</v>
       </c>
       <c r="E267">
         <v>7</v>
       </c>
       <c r="F267" t="s">
-        <v>485</v>
+        <v>495</v>
       </c>
       <c r="G267" t="s">
-        <v>514</v>
+        <v>524</v>
       </c>
       <c r="H267">
         <v>0</v>
@@ -10543,7 +10588,7 @@
         <v>8</v>
       </c>
       <c r="F268" t="s">
-        <v>483</v>
+        <v>493</v>
       </c>
       <c r="G268" t="s">
         <v>320</v>
@@ -10555,7 +10600,7 @@
         <v>8</v>
       </c>
       <c r="J268" t="s">
-        <v>483</v>
+        <v>493</v>
       </c>
     </row>
     <row r="269" spans="1:10">
@@ -10575,7 +10620,7 @@
         <v>8</v>
       </c>
       <c r="F269" t="s">
-        <v>486</v>
+        <v>496</v>
       </c>
       <c r="G269" t="s">
         <v>320</v>
@@ -10587,7 +10632,7 @@
         <v>8</v>
       </c>
       <c r="J269" t="s">
-        <v>486</v>
+        <v>496</v>
       </c>
     </row>
     <row r="270" spans="1:10">
@@ -10601,13 +10646,13 @@
         <v>320</v>
       </c>
       <c r="D270">
-        <v>12.2443</v>
+        <v>12.195</v>
       </c>
       <c r="E270">
         <v>8</v>
       </c>
       <c r="F270" t="s">
-        <v>486</v>
+        <v>496</v>
       </c>
       <c r="G270" t="s">
         <v>320</v>
@@ -10619,7 +10664,7 @@
         <v>8</v>
       </c>
       <c r="J270" t="s">
-        <v>486</v>
+        <v>496</v>
       </c>
     </row>
     <row r="271" spans="1:10">
@@ -10639,7 +10684,7 @@
         <v>14</v>
       </c>
       <c r="F271" t="s">
-        <v>487</v>
+        <v>497</v>
       </c>
       <c r="G271" t="s">
         <v>320</v>
@@ -10651,7 +10696,7 @@
         <v>16</v>
       </c>
       <c r="J271" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
     </row>
     <row r="272" spans="1:10">
@@ -10665,13 +10710,13 @@
         <v>320</v>
       </c>
       <c r="D272">
-        <v>110.0226</v>
+        <v>109.9695</v>
       </c>
       <c r="E272">
         <v>9</v>
       </c>
       <c r="F272" t="s">
-        <v>488</v>
+        <v>498</v>
       </c>
       <c r="G272" t="s">
         <v>320</v>
@@ -10683,7 +10728,7 @@
         <v>9</v>
       </c>
       <c r="J272" t="s">
-        <v>490</v>
+        <v>498</v>
       </c>
     </row>
     <row r="273" spans="1:10">
@@ -10703,7 +10748,7 @@
         <v>7</v>
       </c>
       <c r="F273" t="s">
-        <v>475</v>
+        <v>485</v>
       </c>
       <c r="G273" t="s">
         <v>320</v>
@@ -10715,7 +10760,7 @@
         <v>7</v>
       </c>
       <c r="J273" t="s">
-        <v>475</v>
+        <v>485</v>
       </c>
     </row>
     <row r="274" spans="1:10">
@@ -10729,22 +10774,25 @@
         <v>320</v>
       </c>
       <c r="D274">
-        <v>24.2743</v>
+        <v>24.1844</v>
       </c>
       <c r="E274">
         <v>8</v>
       </c>
       <c r="F274" t="s">
-        <v>444</v>
+        <v>454</v>
       </c>
       <c r="G274" t="s">
-        <v>514</v>
+        <v>320</v>
       </c>
       <c r="H274">
-        <v>0</v>
+        <v>110.4328</v>
       </c>
       <c r="I274">
-        <v>0</v>
+        <v>15</v>
+      </c>
+      <c r="J274" t="s">
+        <v>560</v>
       </c>
     </row>
     <row r="275" spans="1:10">
@@ -10758,13 +10806,13 @@
         <v>320</v>
       </c>
       <c r="D275">
-        <v>60.6302</v>
+        <v>60.5844</v>
       </c>
       <c r="E275">
         <v>9</v>
       </c>
       <c r="F275" t="s">
-        <v>489</v>
+        <v>499</v>
       </c>
       <c r="G275" t="s">
         <v>320</v>
@@ -10776,7 +10824,7 @@
         <v>8</v>
       </c>
       <c r="J275" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
     </row>
     <row r="276" spans="1:10">
@@ -10796,10 +10844,10 @@
         <v>17</v>
       </c>
       <c r="F276" t="s">
-        <v>452</v>
+        <v>460</v>
       </c>
       <c r="G276" t="s">
-        <v>513</v>
+        <v>524</v>
       </c>
       <c r="H276">
         <v>0</v>
@@ -10819,13 +10867,13 @@
         <v>320</v>
       </c>
       <c r="D277">
-        <v>110.048</v>
+        <v>109.9256</v>
       </c>
       <c r="E277">
         <v>9</v>
       </c>
       <c r="F277" t="s">
-        <v>490</v>
+        <v>498</v>
       </c>
       <c r="G277" t="s">
         <v>320</v>
@@ -10837,7 +10885,7 @@
         <v>9</v>
       </c>
       <c r="J277" t="s">
-        <v>490</v>
+        <v>498</v>
       </c>
     </row>
     <row r="278" spans="1:10">
@@ -10857,7 +10905,7 @@
         <v>9</v>
       </c>
       <c r="F278" t="s">
-        <v>453</v>
+        <v>461</v>
       </c>
       <c r="G278" t="s">
         <v>320</v>
@@ -10869,7 +10917,7 @@
         <v>9</v>
       </c>
       <c r="J278" t="s">
-        <v>453</v>
+        <v>461</v>
       </c>
     </row>
     <row r="279" spans="1:10">
@@ -10883,13 +10931,13 @@
         <v>320</v>
       </c>
       <c r="D279">
-        <v>60.6531</v>
+        <v>60.5582</v>
       </c>
       <c r="E279">
         <v>9</v>
       </c>
       <c r="F279" t="s">
-        <v>491</v>
+        <v>500</v>
       </c>
       <c r="G279" t="s">
         <v>320</v>
@@ -10901,7 +10949,7 @@
         <v>8</v>
       </c>
       <c r="J279" t="s">
-        <v>497</v>
+        <v>506</v>
       </c>
     </row>
     <row r="280" spans="1:10">
@@ -10921,7 +10969,7 @@
         <v>14</v>
       </c>
       <c r="F280" t="s">
-        <v>458</v>
+        <v>467</v>
       </c>
       <c r="G280" t="s">
         <v>320</v>
@@ -10933,7 +10981,7 @@
         <v>16</v>
       </c>
       <c r="J280" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="281" spans="1:10">
@@ -10953,7 +11001,7 @@
         <v>10</v>
       </c>
       <c r="F281" t="s">
-        <v>484</v>
+        <v>494</v>
       </c>
       <c r="G281" t="s">
         <v>320</v>
@@ -10965,7 +11013,7 @@
         <v>10</v>
       </c>
       <c r="J281" t="s">
-        <v>484</v>
+        <v>494</v>
       </c>
     </row>
     <row r="282" spans="1:10">
@@ -10979,13 +11027,13 @@
         <v>320</v>
       </c>
       <c r="D282">
-        <v>24.4225</v>
+        <v>24.3264</v>
       </c>
       <c r="E282">
         <v>10</v>
       </c>
       <c r="F282" t="s">
-        <v>484</v>
+        <v>494</v>
       </c>
       <c r="G282" t="s">
         <v>320</v>
@@ -10997,7 +11045,7 @@
         <v>10</v>
       </c>
       <c r="J282" t="s">
-        <v>484</v>
+        <v>494</v>
       </c>
     </row>
     <row r="283" spans="1:10">
@@ -11011,13 +11059,13 @@
         <v>320</v>
       </c>
       <c r="D283">
-        <v>150.3447</v>
+        <v>150.2823</v>
       </c>
       <c r="E283">
         <v>11</v>
       </c>
       <c r="F283" t="s">
-        <v>492</v>
+        <v>501</v>
       </c>
       <c r="G283" t="s">
         <v>320</v>
@@ -11029,7 +11077,7 @@
         <v>11</v>
       </c>
       <c r="J283" t="s">
-        <v>492</v>
+        <v>501</v>
       </c>
     </row>
     <row r="284" spans="1:10">
@@ -11043,22 +11091,25 @@
         <v>320</v>
       </c>
       <c r="D284">
-        <v>54.9147</v>
+        <v>54.7851</v>
       </c>
       <c r="E284">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F284" t="s">
-        <v>493</v>
+        <v>502</v>
       </c>
       <c r="G284" t="s">
-        <v>514</v>
+        <v>320</v>
       </c>
       <c r="H284">
-        <v>0</v>
+        <v>54.7851</v>
       </c>
       <c r="I284">
-        <v>0</v>
+        <v>8</v>
+      </c>
+      <c r="J284" t="s">
+        <v>502</v>
       </c>
     </row>
     <row r="285" spans="1:10">
@@ -11072,22 +11123,25 @@
         <v>320</v>
       </c>
       <c r="D285">
-        <v>54.9074</v>
+        <v>54.7834</v>
       </c>
       <c r="E285">
         <v>8</v>
       </c>
       <c r="F285" t="s">
-        <v>494</v>
+        <v>503</v>
       </c>
       <c r="G285" t="s">
-        <v>514</v>
+        <v>320</v>
       </c>
       <c r="H285">
-        <v>0</v>
+        <v>54.7834</v>
       </c>
       <c r="I285">
-        <v>0</v>
+        <v>8</v>
+      </c>
+      <c r="J285" t="s">
+        <v>503</v>
       </c>
     </row>
     <row r="286" spans="1:10">
@@ -11107,7 +11161,7 @@
         <v>9</v>
       </c>
       <c r="F286" t="s">
-        <v>495</v>
+        <v>504</v>
       </c>
       <c r="G286" t="s">
         <v>320</v>
@@ -11119,7 +11173,7 @@
         <v>23</v>
       </c>
       <c r="J286" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
     </row>
     <row r="287" spans="1:10">
@@ -11139,7 +11193,7 @@
         <v>15</v>
       </c>
       <c r="F287" t="s">
-        <v>496</v>
+        <v>505</v>
       </c>
       <c r="G287" t="s">
         <v>320</v>
@@ -11151,7 +11205,7 @@
         <v>23</v>
       </c>
       <c r="J287" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
     </row>
     <row r="288" spans="1:10">
@@ -11171,7 +11225,7 @@
         <v>8</v>
       </c>
       <c r="F288" t="s">
-        <v>497</v>
+        <v>506</v>
       </c>
       <c r="G288" t="s">
         <v>320</v>
@@ -11183,7 +11237,7 @@
         <v>8</v>
       </c>
       <c r="J288" t="s">
-        <v>497</v>
+        <v>506</v>
       </c>
     </row>
     <row r="289" spans="1:10">
@@ -11203,7 +11257,7 @@
         <v>10</v>
       </c>
       <c r="F289" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="G289" t="s">
         <v>320</v>
@@ -11215,7 +11269,7 @@
         <v>10</v>
       </c>
       <c r="J289" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="290" spans="1:10">
@@ -11235,10 +11289,10 @@
         <v>17</v>
       </c>
       <c r="F290" t="s">
-        <v>498</v>
+        <v>507</v>
       </c>
       <c r="G290" t="s">
-        <v>513</v>
+        <v>524</v>
       </c>
       <c r="H290">
         <v>0</v>
@@ -11264,7 +11318,7 @@
         <v>11</v>
       </c>
       <c r="F291" t="s">
-        <v>499</v>
+        <v>508</v>
       </c>
       <c r="G291" t="s">
         <v>320</v>
@@ -11276,7 +11330,7 @@
         <v>9</v>
       </c>
       <c r="J291" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
     </row>
     <row r="292" spans="1:10">
@@ -11290,22 +11344,25 @@
         <v>320</v>
       </c>
       <c r="D292">
-        <v>54.9108</v>
+        <v>54.7729</v>
       </c>
       <c r="E292">
         <v>9</v>
       </c>
       <c r="F292" t="s">
-        <v>500</v>
+        <v>509</v>
       </c>
       <c r="G292" t="s">
-        <v>514</v>
+        <v>320</v>
       </c>
       <c r="H292">
-        <v>0</v>
+        <v>54.7729</v>
       </c>
       <c r="I292">
-        <v>0</v>
+        <v>9</v>
+      </c>
+      <c r="J292" t="s">
+        <v>509</v>
       </c>
     </row>
     <row r="293" spans="1:10">
@@ -11325,7 +11382,7 @@
         <v>23</v>
       </c>
       <c r="F293" t="s">
-        <v>501</v>
+        <v>510</v>
       </c>
       <c r="G293" t="s">
         <v>320</v>
@@ -11337,7 +11394,7 @@
         <v>23</v>
       </c>
       <c r="J293" t="s">
-        <v>501</v>
+        <v>510</v>
       </c>
     </row>
     <row r="294" spans="1:10">
@@ -11357,7 +11414,7 @@
         <v>23</v>
       </c>
       <c r="F294" t="s">
-        <v>502</v>
+        <v>511</v>
       </c>
       <c r="G294" t="s">
         <v>320</v>
@@ -11369,7 +11426,7 @@
         <v>23</v>
       </c>
       <c r="J294" t="s">
-        <v>502</v>
+        <v>511</v>
       </c>
     </row>
     <row r="295" spans="1:10">
@@ -11383,13 +11440,13 @@
         <v>320</v>
       </c>
       <c r="D295">
-        <v>4.8046</v>
+        <v>4.7671</v>
       </c>
       <c r="E295">
         <v>6</v>
       </c>
       <c r="F295" t="s">
-        <v>503</v>
+        <v>512</v>
       </c>
       <c r="G295" t="s">
         <v>320</v>
@@ -11401,7 +11458,7 @@
         <v>6</v>
       </c>
       <c r="J295" t="s">
-        <v>503</v>
+        <v>512</v>
       </c>
     </row>
     <row r="296" spans="1:10">
@@ -11415,13 +11472,13 @@
         <v>320</v>
       </c>
       <c r="D296">
-        <v>73.398</v>
+        <v>73.35039999999999</v>
       </c>
       <c r="E296">
         <v>10</v>
       </c>
       <c r="F296" t="s">
-        <v>504</v>
+        <v>513</v>
       </c>
       <c r="G296" t="s">
         <v>320</v>
@@ -11433,7 +11490,7 @@
         <v>10</v>
       </c>
       <c r="J296" t="s">
-        <v>580</v>
+        <v>513</v>
       </c>
     </row>
     <row r="297" spans="1:10">
@@ -11453,7 +11510,7 @@
         <v>11</v>
       </c>
       <c r="F297" t="s">
-        <v>492</v>
+        <v>501</v>
       </c>
       <c r="G297" t="s">
         <v>320</v>
@@ -11465,7 +11522,7 @@
         <v>11</v>
       </c>
       <c r="J297" t="s">
-        <v>492</v>
+        <v>501</v>
       </c>
     </row>
     <row r="298" spans="1:10">
@@ -11479,13 +11536,13 @@
         <v>320</v>
       </c>
       <c r="D298">
-        <v>0.7441</v>
+        <v>0.6794</v>
       </c>
       <c r="E298">
         <v>4</v>
       </c>
       <c r="F298" t="s">
-        <v>505</v>
+        <v>514</v>
       </c>
       <c r="G298" t="s">
         <v>320</v>
@@ -11497,7 +11554,7 @@
         <v>4</v>
       </c>
       <c r="J298" t="s">
-        <v>505</v>
+        <v>514</v>
       </c>
     </row>
     <row r="299" spans="1:10">
@@ -11517,7 +11574,7 @@
         <v>7</v>
       </c>
       <c r="F299" t="s">
-        <v>506</v>
+        <v>515</v>
       </c>
       <c r="G299" t="s">
         <v>320</v>
@@ -11529,7 +11586,7 @@
         <v>7</v>
       </c>
       <c r="J299" t="s">
-        <v>506</v>
+        <v>515</v>
       </c>
     </row>
     <row r="300" spans="1:10">
@@ -11549,16 +11606,19 @@
         <v>17</v>
       </c>
       <c r="F300" t="s">
-        <v>507</v>
+        <v>516</v>
       </c>
       <c r="G300" t="s">
-        <v>514</v>
+        <v>320</v>
       </c>
       <c r="H300">
-        <v>0</v>
+        <v>218.8278</v>
       </c>
       <c r="I300">
-        <v>0</v>
+        <v>17</v>
+      </c>
+      <c r="J300" t="s">
+        <v>516</v>
       </c>
     </row>
     <row r="301" spans="1:10">
@@ -11578,7 +11638,7 @@
         <v>9</v>
       </c>
       <c r="F301" t="s">
-        <v>508</v>
+        <v>517</v>
       </c>
       <c r="G301" t="s">
         <v>320</v>
@@ -11590,7 +11650,7 @@
         <v>23</v>
       </c>
       <c r="J301" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
     </row>
     <row r="302" spans="1:10">
@@ -11604,13 +11664,13 @@
         <v>320</v>
       </c>
       <c r="D302">
-        <v>34.5937</v>
+        <v>34.5643</v>
       </c>
       <c r="E302">
         <v>9</v>
       </c>
       <c r="F302" t="s">
-        <v>379</v>
+        <v>518</v>
       </c>
       <c r="G302" t="s">
         <v>320</v>
@@ -11622,7 +11682,7 @@
         <v>9</v>
       </c>
       <c r="J302" t="s">
-        <v>581</v>
+        <v>518</v>
       </c>
     </row>
     <row r="303" spans="1:10">
@@ -11636,13 +11696,13 @@
         <v>320</v>
       </c>
       <c r="D303">
-        <v>34.6286</v>
+        <v>34.576</v>
       </c>
       <c r="E303">
         <v>9</v>
       </c>
       <c r="F303" t="s">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="G303" t="s">
         <v>320</v>
@@ -11654,7 +11714,7 @@
         <v>9</v>
       </c>
       <c r="J303" t="s">
-        <v>379</v>
+        <v>385</v>
       </c>
     </row>
     <row r="304" spans="1:10">
@@ -11668,13 +11728,13 @@
         <v>320</v>
       </c>
       <c r="D304">
-        <v>0.1454</v>
+        <v>39.9048</v>
       </c>
       <c r="E304">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="F304" t="s">
-        <v>321</v>
+        <v>519</v>
       </c>
       <c r="G304" t="s">
         <v>320</v>
@@ -11686,7 +11746,7 @@
         <v>9</v>
       </c>
       <c r="J304" t="s">
-        <v>582</v>
+        <v>519</v>
       </c>
     </row>
     <row r="305" spans="1:10">
@@ -11700,13 +11760,13 @@
         <v>320</v>
       </c>
       <c r="D305">
-        <v>39.9554</v>
+        <v>39.9137</v>
       </c>
       <c r="E305">
         <v>8</v>
       </c>
       <c r="F305" t="s">
-        <v>381</v>
+        <v>364</v>
       </c>
       <c r="G305" t="s">
         <v>320</v>
@@ -11718,7 +11778,7 @@
         <v>8</v>
       </c>
       <c r="J305" t="s">
-        <v>381</v>
+        <v>364</v>
       </c>
     </row>
     <row r="306" spans="1:10">
@@ -11738,7 +11798,7 @@
         <v>5</v>
       </c>
       <c r="F306" t="s">
-        <v>509</v>
+        <v>520</v>
       </c>
       <c r="G306" t="s">
         <v>320</v>
@@ -11750,7 +11810,7 @@
         <v>5</v>
       </c>
       <c r="J306" t="s">
-        <v>509</v>
+        <v>520</v>
       </c>
     </row>
     <row r="307" spans="1:10">
@@ -11764,13 +11824,13 @@
         <v>320</v>
       </c>
       <c r="D307">
-        <v>51.5375</v>
+        <v>51.4862</v>
       </c>
       <c r="E307">
         <v>5</v>
       </c>
       <c r="F307" t="s">
-        <v>419</v>
+        <v>429</v>
       </c>
       <c r="G307" t="s">
         <v>320</v>
@@ -11782,7 +11842,7 @@
         <v>5</v>
       </c>
       <c r="J307" t="s">
-        <v>419</v>
+        <v>429</v>
       </c>
     </row>
     <row r="308" spans="1:10">
@@ -11799,7 +11859,7 @@
         <v>5</v>
       </c>
       <c r="F308" t="s">
-        <v>510</v>
+        <v>521</v>
       </c>
       <c r="G308" t="s">
         <v>320</v>
@@ -11811,7 +11871,7 @@
         <v>5</v>
       </c>
       <c r="J308" t="s">
-        <v>510</v>
+        <v>521</v>
       </c>
     </row>
     <row r="309" spans="1:10">
@@ -11828,16 +11888,19 @@
         <v>9</v>
       </c>
       <c r="F309" t="s">
-        <v>508</v>
+        <v>517</v>
       </c>
       <c r="G309" t="s">
-        <v>513</v>
+        <v>320</v>
       </c>
       <c r="H309">
-        <v>0</v>
+        <v>243.1446</v>
       </c>
       <c r="I309">
-        <v>0</v>
+        <v>23</v>
+      </c>
+      <c r="J309" t="s">
+        <v>576</v>
       </c>
     </row>
     <row r="310" spans="1:10">
@@ -11854,7 +11917,7 @@
         <v>4</v>
       </c>
       <c r="F310" t="s">
-        <v>511</v>
+        <v>522</v>
       </c>
       <c r="G310" t="s">
         <v>320</v>
@@ -11866,7 +11929,7 @@
         <v>4</v>
       </c>
       <c r="J310" t="s">
-        <v>511</v>
+        <v>522</v>
       </c>
     </row>
     <row r="311" spans="1:10">
@@ -11883,7 +11946,7 @@
         <v>4</v>
       </c>
       <c r="F311" t="s">
-        <v>512</v>
+        <v>523</v>
       </c>
       <c r="G311" t="s">
         <v>320</v>
@@ -11895,7 +11958,7 @@
         <v>4</v>
       </c>
       <c r="J311" t="s">
-        <v>512</v>
+        <v>523</v>
       </c>
     </row>
   </sheetData>
